--- a/src/attributions/attributions_saliency_traj_340.xlsx
+++ b/src/attributions/attributions_saliency_traj_340.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.042792246153113e-05</v>
+        <v>0.04078938812017441</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000105771810922306</v>
+        <v>0.3384112119674683</v>
       </c>
       <c r="C3" t="n">
-        <v>1.824369246605784e-05</v>
+        <v>0.07544499635696411</v>
       </c>
       <c r="D3" t="n">
-        <v>5.400845839176327e-05</v>
+        <v>0.03066695295274258</v>
       </c>
       <c r="E3" t="n">
-        <v>1.462937689211685e-06</v>
+        <v>0.09031637012958527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001381870388286188</v>
+        <v>0.108557254076004</v>
       </c>
       <c r="G3" t="n">
-        <v>1.996555874939077e-05</v>
+        <v>0.002448149025440216</v>
       </c>
       <c r="H3" t="n">
-        <v>4.714667375083081e-05</v>
+        <v>0.02656998671591282</v>
       </c>
       <c r="I3" t="n">
-        <v>1.248886292160023e-05</v>
+        <v>0.04507782682776451</v>
       </c>
       <c r="J3" t="n">
-        <v>4.091020673513412e-05</v>
+        <v>0.0356142520904541</v>
       </c>
       <c r="K3" t="n">
-        <v>8.382221858482808e-05</v>
+        <v>0.4625240564346313</v>
       </c>
       <c r="L3" t="n">
-        <v>2.52641984843649e-05</v>
+        <v>0.0498245470225811</v>
       </c>
       <c r="M3" t="n">
-        <v>4.572828765958548e-05</v>
+        <v>0.07534864544868469</v>
       </c>
       <c r="N3" t="n">
-        <v>3.76620446331799e-05</v>
+        <v>0.1621222198009491</v>
       </c>
       <c r="O3" t="n">
-        <v>9.191948629450053e-05</v>
+        <v>0.06970874220132828</v>
       </c>
       <c r="P3" t="n">
-        <v>1.959051223821007e-05</v>
+        <v>0.03317595273256302</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.637538844079245e-05</v>
+        <v>0.06388275325298309</v>
       </c>
       <c r="R3" t="n">
-        <v>2.365098680456867e-06</v>
+        <v>0.01506485417485237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.856282096923678e-06</v>
+        <v>2.018176019191742e-06</v>
       </c>
       <c r="T3" t="n">
-        <v>3.63044932782941e-07</v>
+        <v>0.03984662890434265</v>
       </c>
       <c r="U3" t="n">
-        <v>2.127805419149809e-05</v>
+        <v>0.01205381378531456</v>
       </c>
       <c r="V3" t="n">
-        <v>4.278867436369183e-06</v>
+        <v>0.1006731912493706</v>
       </c>
       <c r="W3" t="n">
-        <v>3.144986840197816e-05</v>
+        <v>0.04455775022506714</v>
       </c>
       <c r="X3" t="n">
-        <v>2.313910226803273e-05</v>
+        <v>0.04431780055165291</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.135167051164899e-05</v>
+        <v>0.01642431505024433</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.519690032291692e-06</v>
+        <v>0.05436363443732262</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.473403224546928e-06</v>
+        <v>0.04344098642468452</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.294854130013846e-05</v>
+        <v>0.04233205690979958</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.057292502082419e-05</v>
+        <v>0.0723172053694725</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.592066266515758e-05</v>
+        <v>0.05991659313440323</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.48653789437958e-05</v>
+        <v>0.07258686423301697</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.767152288171928e-06</v>
+        <v>0.09401294589042664</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.389941371598979e-05</v>
+        <v>0.03808954358100891</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.378906836180249e-05</v>
+        <v>0.003193152137100697</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.527415042801294e-05</v>
+        <v>0.1362303793430328</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.961667658179067e-05</v>
+        <v>0.02696070447564125</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.91373001143802e-05</v>
+        <v>0.02304375171661377</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.134652939072112e-05</v>
+        <v>0.1179238855838776</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.293424429604784e-05</v>
+        <v>0.05865663290023804</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.425485601837863e-06</v>
+        <v>0.02342182770371437</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.506143209757283e-05</v>
+        <v>0.08153390884399414</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.020461917913053e-05</v>
+        <v>0.03013264574110508</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.11877488961909e-05</v>
+        <v>0.04192600771784782</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.426124592602719e-05</v>
+        <v>0.03572534024715424</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.355311143124709e-06</v>
+        <v>0.03823817148804665</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.415586994990008e-06</v>
+        <v>0.03438834100961685</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.540527490666136e-05</v>
+        <v>0.4120301306247711</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.846098348323721e-05</v>
+        <v>0.002479478716850281</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.248869688832201e-05</v>
+        <v>0.005217906553298235</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.475819539744407e-05</v>
+        <v>0.06790550053119659</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.128118108492345e-05</v>
+        <v>0.085393987596035</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.414222737774253e-05</v>
+        <v>0.0237553957849741</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.059114977892023e-06</v>
+        <v>0.04971828684210777</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.728722963889595e-05</v>
+        <v>0.03378244116902351</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.827754310099408e-06</v>
+        <v>0.02116158604621887</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.264985182089731e-05</v>
+        <v>0.1359228193759918</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.165261710411869e-05</v>
+        <v>0.05620453506708145</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.498637397569837e-06</v>
+        <v>0.02625179477035999</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.101828254642896e-06</v>
+        <v>0.0662754625082016</v>
       </c>
       <c r="BH3" t="n">
-        <v>1.401753434038255e-05</v>
+        <v>0.023111741989851</v>
       </c>
       <c r="BI3" t="n">
-        <v>9.461638910579495e-06</v>
+        <v>0.06351277232170105</v>
       </c>
       <c r="BJ3" t="n">
-        <v>4.72442388854688e-06</v>
+        <v>0.03430302068591118</v>
       </c>
       <c r="BK3" t="n">
-        <v>3.9338647184195e-07</v>
+        <v>0.002931220456957817</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.293028435611632e-05</v>
+        <v>0.04776667058467865</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.019136445596814e-05</v>
+        <v>0.01269954442977905</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.226579661306459e-05</v>
+        <v>0.002524926792830229</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.65781493706163e-05</v>
+        <v>0.01999948173761368</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.566833467833931e-06</v>
+        <v>0.03327328339219093</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.238474578713067e-05</v>
+        <v>0.0275725070387125</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.204364343720954e-05</v>
+        <v>0.1342823654413223</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.953098924597725e-06</v>
+        <v>0.003470718860626221</v>
       </c>
       <c r="BT3" t="n">
-        <v>1.66056943271542e-05</v>
+        <v>0.01485249679535627</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.131364570028381e-05</v>
+        <v>0.0113902622833848</v>
       </c>
       <c r="BV3" t="n">
-        <v>3.134147482342087e-05</v>
+        <v>0.2317816913127899</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.826908555813134e-05</v>
+        <v>0.05140302330255508</v>
       </c>
       <c r="BX3" t="n">
-        <v>2.585356560302898e-05</v>
+        <v>0.06420478224754333</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.649207843001932e-05</v>
+        <v>0.04126279056072235</v>
       </c>
       <c r="BZ3" t="n">
-        <v>5.173881800146773e-05</v>
+        <v>0.07726077735424042</v>
       </c>
       <c r="CA3" t="n">
-        <v>5.254887128103292e-06</v>
+        <v>0.04594900086522102</v>
       </c>
       <c r="CB3" t="n">
-        <v>6.756889888492879e-06</v>
+        <v>0.01241929363459349</v>
       </c>
       <c r="CC3" t="n">
-        <v>1.06160769064445e-07</v>
+        <v>0.03789399564266205</v>
       </c>
       <c r="CD3" t="n">
-        <v>9.457174201088492e-06</v>
+        <v>0.001761535531841218</v>
       </c>
       <c r="CE3" t="n">
-        <v>6.46867238174309e-06</v>
+        <v>0.1321179866790771</v>
       </c>
       <c r="CF3" t="n">
-        <v>5.101519036543323e-06</v>
+        <v>0.007349908351898193</v>
       </c>
       <c r="CG3" t="n">
-        <v>5.129976216267096e-06</v>
+        <v>0.01445725560188293</v>
       </c>
       <c r="CH3" t="n">
-        <v>8.427743523498066e-06</v>
+        <v>0.01281611621379852</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.992679972318001e-05</v>
+        <v>0.0437309518456459</v>
       </c>
       <c r="CJ3" t="n">
-        <v>5.78424078412354e-06</v>
+        <v>0.0276423841714859</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.279553453059634e-05</v>
+        <v>0.0005199802108108997</v>
       </c>
       <c r="CL3" t="n">
-        <v>3.484640274109552e-07</v>
+        <v>0.003772380761802197</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.29493073472986e-05</v>
+        <v>0.06957223266363144</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.458261635889357e-07</v>
+        <v>0.191702738404274</v>
       </c>
       <c r="CO3" t="n">
-        <v>9.022801350511145e-06</v>
+        <v>0.0553075447678566</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.244854047399713e-05</v>
+        <v>0.03085131384432316</v>
       </c>
       <c r="CQ3" t="n">
-        <v>1.195391814690083e-05</v>
+        <v>0.05309325829148293</v>
       </c>
       <c r="CR3" t="n">
-        <v>6.311712240858469e-06</v>
+        <v>0.03843044862151146</v>
       </c>
       <c r="CS3" t="n">
-        <v>1.655826963542495e-06</v>
+        <v>0.03379889205098152</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.098818913509604e-05</v>
+        <v>0.01537466514855623</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.577384682605043e-05</v>
+        <v>0.003493008203804493</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.953066086774925e-06</v>
+        <v>0.01893440261483192</v>
       </c>
       <c r="CW3" t="n">
-        <v>9.761155524756759e-06</v>
+        <v>0.1299120783805847</v>
       </c>
       <c r="CX3" t="n">
-        <v>4.915202680422226e-06</v>
+        <v>0.01045121531933546</v>
       </c>
       <c r="CY3" t="n">
-        <v>7.879163604229689e-06</v>
+        <v>0.002289107069373131</v>
       </c>
       <c r="CZ3" t="n">
-        <v>6.802786174375797e-07</v>
+        <v>0.00599029241129756</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.311584103154019e-05</v>
+        <v>0.04936012253165245</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.341510025871685e-06</v>
+        <v>0.01185767538845539</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.890497878775932e-05</v>
+        <v>0.003384734503924847</v>
       </c>
       <c r="DD3" t="n">
-        <v>1.249381966772489e-07</v>
+        <v>0.01351596787571907</v>
       </c>
       <c r="DE3" t="n">
-        <v>1.450094532629009e-05</v>
+        <v>0.06556370854377747</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.574895395606291e-05</v>
+        <v>0.03938791900873184</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.056584733305499e-05</v>
+        <v>0.008322076871991158</v>
       </c>
       <c r="DH3" t="n">
-        <v>3.803571962635033e-05</v>
+        <v>0.005744811147451401</v>
       </c>
       <c r="DI3" t="n">
-        <v>2.99397961498471e-05</v>
+        <v>0.07981002330780029</v>
       </c>
       <c r="DJ3" t="n">
-        <v>9.825348570302594e-07</v>
+        <v>0.05019736289978027</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.126449650560971e-06</v>
+        <v>0.02809742093086243</v>
       </c>
       <c r="DL3" t="n">
-        <v>5.355203029466793e-05</v>
+        <v>0.004649551585316658</v>
       </c>
       <c r="DM3" t="n">
-        <v>1.730318217596505e-05</v>
+        <v>0.00885315053164959</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.257858366443543e-05</v>
+        <v>0.04070524871349335</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.188819987874012e-05</v>
+        <v>0.06203920021653175</v>
       </c>
       <c r="DP3" t="n">
-        <v>1.557489849801641e-05</v>
+        <v>0.01118872687220573</v>
       </c>
       <c r="DQ3" t="n">
-        <v>6.84770520820166e-06</v>
+        <v>0.0582011379301548</v>
       </c>
       <c r="DR3" t="n">
-        <v>1.362713010166772e-05</v>
+        <v>0.01772676780819893</v>
       </c>
       <c r="DS3" t="n">
-        <v>5.186933549339301e-07</v>
+        <v>0.006301060784608126</v>
       </c>
       <c r="DT3" t="n">
-        <v>9.7571237347438e-06</v>
+        <v>0.01563463173806667</v>
       </c>
       <c r="DU3" t="n">
-        <v>6.904715519340243e-06</v>
+        <v>0.06417970359325409</v>
       </c>
       <c r="DV3" t="n">
-        <v>3.069629428864573e-06</v>
+        <v>0.02899842336773872</v>
       </c>
       <c r="DW3" t="n">
-        <v>1.302226792176953e-06</v>
+        <v>0.04395903646945953</v>
       </c>
       <c r="DX3" t="n">
-        <v>3.317550408610259e-06</v>
+        <v>0.07234892994165421</v>
       </c>
       <c r="DY3" t="n">
-        <v>1.748368958942592e-06</v>
+        <v>0.02219946309924126</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.533180304453708e-05</v>
+        <v>0.01683271490037441</v>
       </c>
       <c r="EA3" t="n">
-        <v>2.028126073128078e-05</v>
+        <v>0.02763549983501434</v>
       </c>
       <c r="EB3" t="n">
-        <v>7.653416105313227e-06</v>
+        <v>0.1323626935482025</v>
       </c>
       <c r="EC3" t="n">
-        <v>1.730328222038224e-06</v>
+        <v>0.001548888627439737</v>
       </c>
       <c r="ED3" t="n">
-        <v>1.9078512195847e-05</v>
+        <v>0.04189076647162437</v>
       </c>
       <c r="EE3" t="n">
-        <v>1.38069356125925e-06</v>
+        <v>0.01253638975322247</v>
       </c>
       <c r="EF3" t="n">
-        <v>1.55196948981029e-06</v>
+        <v>0.003069348633289337</v>
       </c>
       <c r="EG3" t="n">
-        <v>2.096168373100227e-06</v>
+        <v>0.05930996313691139</v>
       </c>
       <c r="EH3" t="n">
-        <v>9.354299436381552e-06</v>
+        <v>0.006532507948577404</v>
       </c>
       <c r="EI3" t="n">
-        <v>1.976334260689327e-06</v>
+        <v>0.06257405132055283</v>
       </c>
       <c r="EJ3" t="n">
-        <v>2.764701093838084e-06</v>
+        <v>0.003864966565743089</v>
       </c>
       <c r="EK3" t="n">
-        <v>2.318313636351377e-05</v>
+        <v>0.0124969445168972</v>
       </c>
       <c r="EL3" t="n">
-        <v>5.222595063969493e-06</v>
+        <v>0.001145257148891687</v>
       </c>
       <c r="EM3" t="n">
-        <v>1.001954387902515e-05</v>
+        <v>0.004383237101137638</v>
       </c>
       <c r="EN3" t="n">
-        <v>5.960322596365586e-06</v>
+        <v>0.008759846910834312</v>
       </c>
       <c r="EO3" t="n">
-        <v>9.979153219319414e-07</v>
+        <v>0.01782970316708088</v>
       </c>
       <c r="EP3" t="n">
-        <v>1.709444859443465e-06</v>
+        <v>0.07405043393373489</v>
       </c>
       <c r="EQ3" t="n">
-        <v>5.687570592272095e-06</v>
+        <v>0.0090671731159091</v>
       </c>
       <c r="ER3" t="n">
-        <v>1.232497561431956e-05</v>
+        <v>0.03308206796646118</v>
       </c>
       <c r="ES3" t="n">
-        <v>1.751274339767406e-06</v>
+        <v>0.02015794813632965</v>
       </c>
       <c r="ET3" t="n">
-        <v>1.168383641925175e-05</v>
+        <v>0.007213807664811611</v>
       </c>
       <c r="EU3" t="n">
-        <v>8.613375030108728e-06</v>
+        <v>0.03752023726701736</v>
       </c>
       <c r="EV3" t="n">
-        <v>4.19731586589478e-05</v>
+        <v>0.01278405543416739</v>
       </c>
       <c r="EW3" t="n">
-        <v>2.349460373807233e-06</v>
+        <v>0.01259783189743757</v>
       </c>
       <c r="EX3" t="n">
-        <v>5.079425136500504e-06</v>
+        <v>0.0132734514772892</v>
       </c>
       <c r="EY3" t="n">
-        <v>5.181531832931796e-06</v>
+        <v>0.1491728276014328</v>
       </c>
       <c r="EZ3" t="n">
-        <v>7.74904947320465e-07</v>
+        <v>0.005302363075315952</v>
       </c>
       <c r="FA3" t="n">
-        <v>5.609025720332284e-06</v>
+        <v>0.007852122187614441</v>
       </c>
       <c r="FB3" t="n">
-        <v>2.464437557136989e-06</v>
+        <v>0.01262987591326237</v>
       </c>
       <c r="FC3" t="n">
-        <v>1.701364817563444e-05</v>
+        <v>0.04522288963198662</v>
       </c>
       <c r="FD3" t="n">
-        <v>7.974002073751763e-06</v>
+        <v>0.02786237187683582</v>
       </c>
       <c r="FE3" t="n">
-        <v>1.373038958263351e-05</v>
+        <v>0.007105983793735504</v>
       </c>
       <c r="FF3" t="n">
-        <v>1.061872808350017e-06</v>
+        <v>0.01560706738382578</v>
       </c>
       <c r="FG3" t="n">
-        <v>4.75679325973033e-06</v>
+        <v>0.02308074757456779</v>
       </c>
       <c r="FH3" t="n">
-        <v>1.467411220801296e-05</v>
+        <v>0.06722891330718994</v>
       </c>
       <c r="FI3" t="n">
-        <v>9.793062417884357e-06</v>
+        <v>0.04169682413339615</v>
       </c>
       <c r="FJ3" t="n">
-        <v>4.243012153892778e-05</v>
+        <v>0.06389907747507095</v>
       </c>
       <c r="FK3" t="n">
-        <v>1.140187850978691e-05</v>
+        <v>0.06401766091585159</v>
       </c>
       <c r="FL3" t="n">
-        <v>2.538342596380971e-05</v>
+        <v>0.003785191103816032</v>
       </c>
       <c r="FM3" t="n">
-        <v>1.163725664810045e-05</v>
+        <v>0.03791634365916252</v>
       </c>
       <c r="FN3" t="n">
-        <v>1.45693829836091e-05</v>
+        <v>0.03795735910534859</v>
       </c>
       <c r="FO3" t="n">
-        <v>1.494907246524235e-05</v>
+        <v>0.05887401103973389</v>
       </c>
       <c r="FP3" t="n">
-        <v>1.063760555553017e-05</v>
+        <v>0.1310753673315048</v>
       </c>
       <c r="FQ3" t="n">
-        <v>6.059245788492262e-05</v>
+        <v>0.1605139672756195</v>
       </c>
       <c r="FR3" t="n">
-        <v>6.324492915155133e-06</v>
+        <v>0.09078575670719147</v>
       </c>
       <c r="FS3" t="n">
-        <v>3.670053774840198e-05</v>
+        <v>0.09045471996068954</v>
       </c>
       <c r="FT3" t="n">
-        <v>3.063804615521803e-05</v>
+        <v>0.0604013130068779</v>
       </c>
       <c r="FU3" t="n">
-        <v>3.913442196790129e-05</v>
+        <v>0.1094101592898369</v>
       </c>
       <c r="FV3" t="n">
-        <v>1.817967495298944e-05</v>
+        <v>0.01057599298655987</v>
       </c>
       <c r="FW3" t="n">
-        <v>4.18377294408856e-06</v>
+        <v>0.03683409094810486</v>
       </c>
       <c r="FX3" t="n">
-        <v>5.074835485174845e-07</v>
+        <v>0.04113928973674774</v>
       </c>
       <c r="FY3" t="n">
-        <v>1.413526842952706e-05</v>
+        <v>0.0218859538435936</v>
       </c>
       <c r="FZ3" t="n">
-        <v>4.176616585027659e-06</v>
+        <v>0.03440693020820618</v>
       </c>
       <c r="GA3" t="n">
-        <v>1.074058855010662e-05</v>
+        <v>0.03972222656011581</v>
       </c>
       <c r="GB3" t="n">
-        <v>6.147763997432776e-06</v>
+        <v>0.06114685907959938</v>
       </c>
       <c r="GC3" t="n">
-        <v>3.914928674930707e-05</v>
+        <v>0.02698884904384613</v>
       </c>
       <c r="GD3" t="n">
-        <v>1.990911641769344e-06</v>
+        <v>0.003471802920103073</v>
       </c>
       <c r="GE3" t="n">
-        <v>3.33746756950859e-05</v>
+        <v>0.02506741881370544</v>
       </c>
       <c r="GF3" t="n">
-        <v>1.907231489894912e-05</v>
+        <v>0.04287133738398552</v>
       </c>
       <c r="GG3" t="n">
-        <v>9.888306522043422e-06</v>
+        <v>0.03593862801790237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1.259908954942546e-09</v>
+        <v>0.125170111656189</v>
       </c>
       <c r="B4" t="n">
-        <v>1.444237285319616e-09</v>
+        <v>0.03245106339454651</v>
       </c>
       <c r="C4" t="n">
-        <v>7.867581031106852e-10</v>
+        <v>0.02173539251089096</v>
       </c>
       <c r="D4" t="n">
-        <v>7.912098753948271e-11</v>
+        <v>0.005888589657843113</v>
       </c>
       <c r="E4" t="n">
-        <v>2.269902932283685e-09</v>
+        <v>0.01264751423150301</v>
       </c>
       <c r="F4" t="n">
-        <v>5.774521305568214e-09</v>
+        <v>0.03203550353646278</v>
       </c>
       <c r="G4" t="n">
-        <v>6.826079701482968e-10</v>
+        <v>0.03195583075284958</v>
       </c>
       <c r="H4" t="n">
-        <v>3.036805029665857e-09</v>
+        <v>0.03120711445808411</v>
       </c>
       <c r="I4" t="n">
-        <v>2.792556741404439e-10</v>
+        <v>0.01063968241214752</v>
       </c>
       <c r="J4" t="n">
-        <v>1.467496124618606e-10</v>
+        <v>0.1370189040899277</v>
       </c>
       <c r="K4" t="n">
-        <v>1.151885808958752e-09</v>
+        <v>0.04960399121046066</v>
       </c>
       <c r="L4" t="n">
-        <v>3.729809239239046e-10</v>
+        <v>0.01962910406291485</v>
       </c>
       <c r="M4" t="n">
-        <v>7.189305262222945e-10</v>
+        <v>0.01726522296667099</v>
       </c>
       <c r="N4" t="n">
-        <v>1.182778652797367e-09</v>
+        <v>0.03394317999482155</v>
       </c>
       <c r="O4" t="n">
-        <v>3.887840271943332e-09</v>
+        <v>0.08235538750886917</v>
       </c>
       <c r="P4" t="n">
-        <v>1.081532308155886e-09</v>
+        <v>0.0296458825469017</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.953595590327041e-09</v>
+        <v>0.03770082071423531</v>
       </c>
       <c r="R4" t="n">
-        <v>1.881395872427305e-10</v>
+        <v>0.04667048528790474</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7849477451648e-10</v>
+        <v>0.01632746867835522</v>
       </c>
       <c r="T4" t="n">
-        <v>4.802620523491896e-10</v>
+        <v>0.04947621375322342</v>
       </c>
       <c r="U4" t="n">
-        <v>1.067785096453555e-10</v>
+        <v>0.03491472080349922</v>
       </c>
       <c r="V4" t="n">
-        <v>7.700187154568994e-10</v>
+        <v>0.01604219898581505</v>
       </c>
       <c r="W4" t="n">
-        <v>1.234733093546936e-09</v>
+        <v>0.001531909336335957</v>
       </c>
       <c r="X4" t="n">
-        <v>1.199729759981949e-09</v>
+        <v>0.02642637304961681</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.222056900118673e-10</v>
+        <v>0.01093343831598759</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.815284920274166e-10</v>
+        <v>0.03564249351620674</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.306467794532807e-10</v>
+        <v>0.01823904365301132</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.104986209429455e-10</v>
+        <v>0.02060639299452305</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.736332768322086e-10</v>
+        <v>0.03030149079859257</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.161320484222017e-09</v>
+        <v>0.01795031502842903</v>
       </c>
       <c r="AE4" t="n">
-        <v>9.239671250327319e-10</v>
+        <v>0.00628789933398366</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.844838808968575e-10</v>
+        <v>0.0009893812239170074</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.604676114208559e-11</v>
+        <v>0.0673191174864769</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.873179637598923e-10</v>
+        <v>0.0157710500061512</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.634870348103505e-11</v>
+        <v>0.03141667693853378</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6.99645841262253e-10</v>
+        <v>0.0183519721031189</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.474161514027685e-10</v>
+        <v>0.008062262088060379</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.502189177024718e-10</v>
+        <v>0.03131250292062759</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.630159701144663e-10</v>
+        <v>0.06044848635792732</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.921665380270724e-10</v>
+        <v>0.0413794107735157</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.834407484390681e-10</v>
+        <v>0.03110760822892189</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.3600720549789e-09</v>
+        <v>0.01679731719195843</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.085976084728827e-10</v>
+        <v>0.0205394197255373</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.677414259887883e-11</v>
+        <v>0.004978010896593332</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.732167518424092e-10</v>
+        <v>0.008305681869387627</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.026886464750021e-09</v>
+        <v>0.04422911256551743</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.770335877893103e-09</v>
+        <v>0.003475152421742678</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.144691587830266e-10</v>
+        <v>0.07022437453269958</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.208162347943187e-09</v>
+        <v>0.01201381627470255</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.402196524504575e-09</v>
+        <v>0.02506974339485168</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.203895898058363e-09</v>
+        <v>0.1461832523345947</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.727345595678116e-10</v>
+        <v>0.02253764681518078</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.224581878238155e-10</v>
+        <v>0.03182458505034447</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.554201656261966e-09</v>
+        <v>0.02899019978940487</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.557929365160533e-10</v>
+        <v>0.0179344080388546</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.314154866680298e-10</v>
+        <v>0.08375535160303116</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.965607121512392e-10</v>
+        <v>0.004115313291549683</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.03022768094263e-09</v>
+        <v>0.01721667684614658</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.038761547420222e-10</v>
+        <v>0.01479469053447247</v>
       </c>
       <c r="BH4" t="n">
-        <v>4.862790170534481e-10</v>
+        <v>0.07084779441356659</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.007121275264922e-09</v>
+        <v>0.03445468470454216</v>
       </c>
       <c r="BJ4" t="n">
-        <v>6.174710187600851e-10</v>
+        <v>0.02942744269967079</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.021673523560196e-09</v>
+        <v>0.03463555127382278</v>
       </c>
       <c r="BL4" t="n">
-        <v>8.672695339662084e-10</v>
+        <v>0.06663665175437927</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.714981572893294e-10</v>
+        <v>0.03156857937574387</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.025293680129607e-10</v>
+        <v>0.02841717749834061</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.685510702704619e-10</v>
+        <v>0.008292704820632935</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.148512951409941e-09</v>
+        <v>0.002378633711487055</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.437955724081235e-11</v>
+        <v>0.006604617927223444</v>
       </c>
       <c r="BR4" t="n">
-        <v>5.235636368894347e-10</v>
+        <v>0.01138735376298428</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.545309460039618e-10</v>
+        <v>0.001934349769726396</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.261095672333568e-10</v>
+        <v>0.008192677050828934</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.830475658883614e-10</v>
+        <v>0.01340945530682802</v>
       </c>
       <c r="BV4" t="n">
-        <v>2.32369262720411e-11</v>
+        <v>0.03590461611747742</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.461915948881455e-10</v>
+        <v>0.01466277521103621</v>
       </c>
       <c r="BX4" t="n">
-        <v>5.259311874894479e-10</v>
+        <v>0.01515885349363089</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.024200806971521e-09</v>
+        <v>0.008194449357688427</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.46690801120053e-09</v>
+        <v>0.04012502357363701</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.66915350932706e-10</v>
+        <v>0.03867941349744797</v>
       </c>
       <c r="CB4" t="n">
-        <v>1.161331697474566e-09</v>
+        <v>0.0157112330198288</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.468698773710031e-10</v>
+        <v>0.014380750246346</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.891720287361398e-12</v>
+        <v>0.08385542035102844</v>
       </c>
       <c r="CE4" t="n">
-        <v>4.702688793933874e-10</v>
+        <v>0.01442188024520874</v>
       </c>
       <c r="CF4" t="n">
-        <v>7.89774773357621e-11</v>
+        <v>0.01813642494380474</v>
       </c>
       <c r="CG4" t="n">
-        <v>8.61141435937185e-11</v>
+        <v>0.0102971512824297</v>
       </c>
       <c r="CH4" t="n">
-        <v>8.095579762112948e-12</v>
+        <v>0.009690403938293457</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.057402831960985e-09</v>
+        <v>0.003475142875686288</v>
       </c>
       <c r="CJ4" t="n">
-        <v>5.159043192648483e-10</v>
+        <v>0.01865108869969845</v>
       </c>
       <c r="CK4" t="n">
-        <v>6.880830349942357e-10</v>
+        <v>0.01157036330550909</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.706883245855551e-11</v>
+        <v>0.002414466114714742</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.131669757903353e-11</v>
+        <v>0.06012418866157532</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.105471270079761e-09</v>
+        <v>0.03184599429368973</v>
       </c>
       <c r="CO4" t="n">
-        <v>2.830926326691241e-10</v>
+        <v>0.08088313788175583</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.933370130657863e-09</v>
+        <v>0.03432534262537956</v>
       </c>
       <c r="CQ4" t="n">
-        <v>9.267067668794482e-10</v>
+        <v>0.1039305701851845</v>
       </c>
       <c r="CR4" t="n">
-        <v>5.538967062790334e-10</v>
+        <v>0.01963197998702526</v>
       </c>
       <c r="CS4" t="n">
-        <v>4.735240533015883e-10</v>
+        <v>0.02209965512156487</v>
       </c>
       <c r="CT4" t="n">
-        <v>5.725940832590481e-10</v>
+        <v>0.0450342670083046</v>
       </c>
       <c r="CU4" t="n">
-        <v>8.361865089234755e-10</v>
+        <v>0.04422033205628395</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.174479901695392e-10</v>
+        <v>0.08914337307214737</v>
       </c>
       <c r="CW4" t="n">
-        <v>5.70238301023096e-10</v>
+        <v>0.01746330782771111</v>
       </c>
       <c r="CX4" t="n">
-        <v>7.742928520571013e-11</v>
+        <v>0.002336227335035801</v>
       </c>
       <c r="CY4" t="n">
-        <v>3.51106713147864e-11</v>
+        <v>0.006147026550024748</v>
       </c>
       <c r="CZ4" t="n">
-        <v>1.167375224264688e-10</v>
+        <v>0.008140904828906059</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.159214280122001e-09</v>
+        <v>0.01224684994667768</v>
       </c>
       <c r="DB4" t="n">
-        <v>5.66524882561481e-10</v>
+        <v>0.01582404971122742</v>
       </c>
       <c r="DC4" t="n">
-        <v>9.394072186807989e-10</v>
+        <v>0.003709666198119521</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.268468191068962e-10</v>
+        <v>0.003862121840938926</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.129355498008522e-10</v>
+        <v>0.07161387801170349</v>
       </c>
       <c r="DF4" t="n">
-        <v>7.662871448488318e-10</v>
+        <v>0.02084406837821007</v>
       </c>
       <c r="DG4" t="n">
-        <v>6.7864425190578e-10</v>
+        <v>0.06028866022825241</v>
       </c>
       <c r="DH4" t="n">
-        <v>1.878524669152171e-09</v>
+        <v>0.03124360926449299</v>
       </c>
       <c r="DI4" t="n">
-        <v>2.100147389327844e-09</v>
+        <v>0.04761447757482529</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.405128791098775e-10</v>
+        <v>0.009934824891388416</v>
       </c>
       <c r="DK4" t="n">
-        <v>7.048863714942399e-10</v>
+        <v>0.002082665916532278</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.991383280497416e-09</v>
+        <v>0.02434553205966949</v>
       </c>
       <c r="DM4" t="n">
-        <v>2.000802717949668e-10</v>
+        <v>0.04246801882982254</v>
       </c>
       <c r="DN4" t="n">
-        <v>3.703345963224081e-10</v>
+        <v>0.05554315820336342</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.845347902262873e-10</v>
+        <v>0.02006274834275246</v>
       </c>
       <c r="DP4" t="n">
-        <v>4.981297041517507e-10</v>
+        <v>0.06654106080532074</v>
       </c>
       <c r="DQ4" t="n">
-        <v>2.285757000342059e-10</v>
+        <v>0.01918394863605499</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.222809353773613e-10</v>
+        <v>0.03254687786102295</v>
       </c>
       <c r="DS4" t="n">
-        <v>4.578885048900361e-10</v>
+        <v>0.04349057748913765</v>
       </c>
       <c r="DT4" t="n">
-        <v>2.0297971636829e-10</v>
+        <v>0.04344065114855766</v>
       </c>
       <c r="DU4" t="n">
-        <v>2.62371735448852e-10</v>
+        <v>0.0220709927380085</v>
       </c>
       <c r="DV4" t="n">
-        <v>6.424297205320784e-11</v>
+        <v>0.01361064240336418</v>
       </c>
       <c r="DW4" t="n">
-        <v>4.534429776104076e-10</v>
+        <v>0.0141703886911273</v>
       </c>
       <c r="DX4" t="n">
-        <v>4.062889469302888e-10</v>
+        <v>0.04024067521095276</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.955500785390313e-10</v>
+        <v>0.01580602489411831</v>
       </c>
       <c r="DZ4" t="n">
-        <v>7.14390047118485e-10</v>
+        <v>0.02944300137460232</v>
       </c>
       <c r="EA4" t="n">
-        <v>6.881395453461892e-10</v>
+        <v>0.09614157676696777</v>
       </c>
       <c r="EB4" t="n">
-        <v>5.875594455417854e-10</v>
+        <v>0.02298477292060852</v>
       </c>
       <c r="EC4" t="n">
-        <v>4.585325730221967e-10</v>
+        <v>0.01220567245036364</v>
       </c>
       <c r="ED4" t="n">
-        <v>1.040957542386423e-09</v>
+        <v>0.0126319844275713</v>
       </c>
       <c r="EE4" t="n">
-        <v>3.698116812778096e-11</v>
+        <v>0.01165666803717613</v>
       </c>
       <c r="EF4" t="n">
-        <v>5.11542613823579e-11</v>
+        <v>0.06780321896076202</v>
       </c>
       <c r="EG4" t="n">
-        <v>5.868716068668789e-10</v>
+        <v>0.0295090340077877</v>
       </c>
       <c r="EH4" t="n">
-        <v>1.829265627861787e-10</v>
+        <v>0.02639565989375114</v>
       </c>
       <c r="EI4" t="n">
-        <v>7.807643420676413e-10</v>
+        <v>0.01524573285132647</v>
       </c>
       <c r="EJ4" t="n">
-        <v>8.610111512652452e-10</v>
+        <v>0.0115991597995162</v>
       </c>
       <c r="EK4" t="n">
-        <v>6.027878751702076e-10</v>
+        <v>0.007120310794562101</v>
       </c>
       <c r="EL4" t="n">
-        <v>8.811160134847285e-12</v>
+        <v>0.01519463770091534</v>
       </c>
       <c r="EM4" t="n">
-        <v>9.540167961175072e-11</v>
+        <v>0.00777885690331459</v>
       </c>
       <c r="EN4" t="n">
-        <v>4.959623267630775e-10</v>
+        <v>0.01179764047265053</v>
       </c>
       <c r="EO4" t="n">
-        <v>5.156916560444813e-10</v>
+        <v>0.06345149129629135</v>
       </c>
       <c r="EP4" t="n">
-        <v>9.275294421406954e-11</v>
+        <v>0.03184117376804352</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.089425910594244e-10</v>
+        <v>0.0008934687939472497</v>
       </c>
       <c r="ER4" t="n">
-        <v>3.911551638147159e-11</v>
+        <v>0.06036099046468735</v>
       </c>
       <c r="ES4" t="n">
-        <v>2.643460450535429e-11</v>
+        <v>0.003537211334332824</v>
       </c>
       <c r="ET4" t="n">
-        <v>1.210393119066566e-09</v>
+        <v>0.006571217905730009</v>
       </c>
       <c r="EU4" t="n">
-        <v>6.07062122792712e-10</v>
+        <v>6.920809391885996e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>1.242977831772407e-09</v>
+        <v>0.003255048301070929</v>
       </c>
       <c r="EW4" t="n">
-        <v>8.523576289221069e-11</v>
+        <v>0.09705255925655365</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.93077220878024e-10</v>
+        <v>0.08572281897068024</v>
       </c>
       <c r="EY4" t="n">
-        <v>4.443406753651402e-10</v>
+        <v>0.01651212945580482</v>
       </c>
       <c r="EZ4" t="n">
-        <v>2.930773401743636e-10</v>
+        <v>0.01147883664816618</v>
       </c>
       <c r="FA4" t="n">
-        <v>9.502022432772428e-12</v>
+        <v>0.006368263158947229</v>
       </c>
       <c r="FB4" t="n">
-        <v>2.577968047368095e-11</v>
+        <v>0.02872934006154537</v>
       </c>
       <c r="FC4" t="n">
-        <v>9.548033474970907e-10</v>
+        <v>0.01012598164379597</v>
       </c>
       <c r="FD4" t="n">
-        <v>2.729479697816117e-10</v>
+        <v>0.01557329390197992</v>
       </c>
       <c r="FE4" t="n">
-        <v>9.696866642983082e-10</v>
+        <v>0.00278976745903492</v>
       </c>
       <c r="FF4" t="n">
-        <v>3.202088871834263e-10</v>
+        <v>0.005810652393847704</v>
       </c>
       <c r="FG4" t="n">
-        <v>3.401591508467305e-10</v>
+        <v>0.04509497806429863</v>
       </c>
       <c r="FH4" t="n">
-        <v>1.016135731113366e-09</v>
+        <v>0.0227610282599926</v>
       </c>
       <c r="FI4" t="n">
-        <v>7.531856804909864e-10</v>
+        <v>0.007834312506020069</v>
       </c>
       <c r="FJ4" t="n">
-        <v>9.636471620666498e-10</v>
+        <v>0.001552520436234772</v>
       </c>
       <c r="FK4" t="n">
-        <v>7.808447222146242e-10</v>
+        <v>0.02495393715798855</v>
       </c>
       <c r="FL4" t="n">
-        <v>1.043035435799311e-09</v>
+        <v>0.02982068620622158</v>
       </c>
       <c r="FM4" t="n">
-        <v>1.513305869504933e-10</v>
+        <v>0.01434920448809862</v>
       </c>
       <c r="FN4" t="n">
-        <v>1.281388883889178e-10</v>
+        <v>0.00461267726495862</v>
       </c>
       <c r="FO4" t="n">
-        <v>3.478583532334767e-10</v>
+        <v>0.06171008571982384</v>
       </c>
       <c r="FP4" t="n">
-        <v>3.685176330758821e-10</v>
+        <v>0.007246684283018112</v>
       </c>
       <c r="FQ4" t="n">
-        <v>1.171002184108261e-09</v>
+        <v>0.06675706058740616</v>
       </c>
       <c r="FR4" t="n">
-        <v>6.615306913371199e-11</v>
+        <v>0.0330226831138134</v>
       </c>
       <c r="FS4" t="n">
-        <v>1.239030877897562e-09</v>
+        <v>0.07489475607872009</v>
       </c>
       <c r="FT4" t="n">
-        <v>1.168724228506335e-09</v>
+        <v>0.1262443512678146</v>
       </c>
       <c r="FU4" t="n">
-        <v>1.141247429892189e-09</v>
+        <v>0.05121764540672302</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.989887504245559e-11</v>
+        <v>0.008577725850045681</v>
       </c>
       <c r="FW4" t="n">
-        <v>1.632816798435854e-10</v>
+        <v>0.0902426615357399</v>
       </c>
       <c r="FX4" t="n">
-        <v>1.058340082238374e-10</v>
+        <v>0.0684875026345253</v>
       </c>
       <c r="FY4" t="n">
-        <v>3.75374231698089e-10</v>
+        <v>0.05078113451600075</v>
       </c>
       <c r="FZ4" t="n">
-        <v>9.978169679403237e-11</v>
+        <v>0.02093955315649509</v>
       </c>
       <c r="GA4" t="n">
-        <v>2.087131023564837e-10</v>
+        <v>0.0293665137141943</v>
       </c>
       <c r="GB4" t="n">
-        <v>1.495255030903309e-09</v>
+        <v>0.008427394554018974</v>
       </c>
       <c r="GC4" t="n">
-        <v>2.852663882890738e-09</v>
+        <v>0.003399842884391546</v>
       </c>
       <c r="GD4" t="n">
-        <v>4.816144150154855e-10</v>
+        <v>0.0129783358424902</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.03871355960905e-09</v>
+        <v>0.04284312203526497</v>
       </c>
       <c r="GF4" t="n">
-        <v>3.451564034584464e-11</v>
+        <v>0.0205293633043766</v>
       </c>
       <c r="GG4" t="n">
-        <v>1.636746432831515e-10</v>
+        <v>0.05270369350910187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.007801937870681286</v>
+        <v>0.05392231792211533</v>
       </c>
       <c r="B5" t="n">
-        <v>0.005677173845469952</v>
+        <v>0.02123996242880821</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006749969907104969</v>
+        <v>0.2952945828437805</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01097865588963032</v>
+        <v>0.2080222368240356</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002005381044000387</v>
+        <v>0.1559533029794693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003456211648881435</v>
+        <v>0.05164526775479317</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001465666340664029</v>
+        <v>0.006635069847106934</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00543105136603117</v>
+        <v>0.004533305764198303</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005021519027650356</v>
+        <v>0.02271421998739243</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01131905242800713</v>
+        <v>0.03645354509353638</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006182202138006687</v>
+        <v>0.007987946271896362</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006104238331317902</v>
+        <v>0.2639988362789154</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01216486189514399</v>
+        <v>0.156928151845932</v>
       </c>
       <c r="N5" t="n">
-        <v>0.005635800305753946</v>
+        <v>0.2461801916360855</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00082147226203233</v>
+        <v>0.09004217386245728</v>
       </c>
       <c r="P5" t="n">
-        <v>0.003512948751449585</v>
+        <v>0.1329476833343506</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005422930233180523</v>
+        <v>0.03441496938467026</v>
       </c>
       <c r="R5" t="n">
-        <v>0.003931938204914331</v>
+        <v>0.03091197460889816</v>
       </c>
       <c r="S5" t="n">
-        <v>0.003375483443960547</v>
+        <v>0.03021208569407463</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00142701412551105</v>
+        <v>0.09180696308612823</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001289481442654505</v>
+        <v>0.03519128635525703</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0006932829855941236</v>
+        <v>0.07422930002212524</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00584928784519434</v>
+        <v>0.02913414128124714</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001459755352698267</v>
+        <v>0.1285802274942398</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.517139703035355e-06</v>
+        <v>0.03792713209986687</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.008203824050724506</v>
+        <v>0.03672076389193535</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0003445188922341913</v>
+        <v>0.03453348577022552</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0003837207332253456</v>
+        <v>0.01411152817308903</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.004625220317393541</v>
+        <v>0.01782541163265705</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0002666443469934165</v>
+        <v>0.122443363070488</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001368671422824264</v>
+        <v>0.08429104089736938</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001514922827482224</v>
+        <v>0.0381297692656517</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001885236823000014</v>
+        <v>0.07386209070682526</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0006887773051857948</v>
+        <v>0.05907509103417397</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0007779216393828392</v>
+        <v>0.1513333320617676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.001386235351674259</v>
+        <v>0.05845963582396507</v>
       </c>
       <c r="AK5" t="n">
-        <v>3.302283585071564e-05</v>
+        <v>0.05911435559391975</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.00211192574352026</v>
+        <v>0.07060717046260834</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.00074491195846349</v>
+        <v>0.04140763729810715</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0008011626778170466</v>
+        <v>0.0942702442407608</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.0001656215026741847</v>
+        <v>0.01611237227916718</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.001147506292909384</v>
+        <v>0.07172250747680664</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.00224292790517211</v>
+        <v>0.002990813925862312</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.00158946099691093</v>
+        <v>0.03746229037642479</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0003815932141151279</v>
+        <v>0.01671123877167702</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.001120291068218648</v>
+        <v>0.09112760424613953</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.00108147703576833</v>
+        <v>0.06209618970751762</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.003734180238097906</v>
+        <v>0.2885023057460785</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.007894637063145638</v>
+        <v>0.1770698130130768</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001156045356765389</v>
+        <v>0.1727557182312012</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.003563028061762452</v>
+        <v>0.07320402562618256</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0002066822489723563</v>
+        <v>0.1021123379468918</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.0048289829865098</v>
+        <v>0.02984070032835007</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.003033931832760572</v>
+        <v>0.04916224256157875</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.01060706377029419</v>
+        <v>0.1023750752210617</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.003178103361278772</v>
+        <v>0.01922401413321495</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.19979878643062e-05</v>
+        <v>0.02465573325753212</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.002386379288509488</v>
+        <v>0.06584601104259491</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.007700564339756966</v>
+        <v>0.1122931391000748</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.001805060426704586</v>
+        <v>0.01841603219509125</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.007746320683509111</v>
+        <v>0.004850706085562706</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.01201037876307964</v>
+        <v>0.05304461345076561</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0003270056913606822</v>
+        <v>0.06525248289108276</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.00173860031645745</v>
+        <v>0.02339128404855728</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.003566642757505178</v>
+        <v>0.03313422203063965</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.00309512228704989</v>
+        <v>0.01980217173695564</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.003044846933335066</v>
+        <v>0.07529713958501816</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.005026108585298061</v>
+        <v>0.01191539689898491</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.002052502939477563</v>
+        <v>0.07615409046411514</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.002530086087062955</v>
+        <v>0.03678403422236443</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0009943443583324552</v>
+        <v>0.01986896619200706</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0019066222012043</v>
+        <v>0.003339893650263548</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001240032725036144</v>
+        <v>0.002067593391984701</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001971015706658363</v>
+        <v>0.0852445662021637</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.002350528491660953</v>
+        <v>0.1243163645267487</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.004107744432985783</v>
+        <v>0.08200258016586304</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001845373073592782</v>
+        <v>0.08273573964834213</v>
       </c>
       <c r="BZ5" t="n">
-        <v>4.103269020561129e-05</v>
+        <v>0.01454275101423264</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.002355578122660518</v>
+        <v>0.08804941177368164</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.008017970249056816</v>
+        <v>0.02121524885296822</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.003882249118760228</v>
+        <v>0.006218843162059784</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001702036708593369</v>
+        <v>0.02392603084445</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.001915368833579123</v>
+        <v>0.0287683866918087</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.001959143904969096</v>
+        <v>0.06548225879669189</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.00245570600964129</v>
+        <v>0.01019670069217682</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001492974581196904</v>
+        <v>0.07567645609378815</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001297491602599621</v>
+        <v>0.00374961644411087</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.001331371255218983</v>
+        <v>0.02350334823131561</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001779967220500112</v>
+        <v>0.002555115148425102</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.001749317394569516</v>
+        <v>0.006500855088233948</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.004513854160904884</v>
+        <v>0.05236145108938217</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0008694101125001907</v>
+        <v>0.05828403681516647</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0001157112783403136</v>
+        <v>0.01424845494329929</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.001262540463358164</v>
+        <v>0.1882976889610291</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.002070171060040593</v>
+        <v>0.2493847608566284</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.001139045925810933</v>
+        <v>0.05454518273472786</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001173903001472354</v>
+        <v>0.03875124081969261</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.001246217871084809</v>
+        <v>0.02190910279750824</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001997432671487331</v>
+        <v>0.01318632066249847</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.001738139661028981</v>
+        <v>0.03614622354507446</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.001271712593734264</v>
+        <v>0.01277123112231493</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.000741566822398454</v>
+        <v>0.07150843739509583</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.001598072936758399</v>
+        <v>0.002848755568265915</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.001027798047289252</v>
+        <v>0.06512946635484695</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0006668125279247761</v>
+        <v>0.01528674736618996</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0006105287466198206</v>
+        <v>0.01953366957604885</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001572398585267365</v>
+        <v>0.0173814669251442</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.00226239301264286</v>
+        <v>0.01959139667451382</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0004981120582669973</v>
+        <v>0.01268593780696392</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.009368604049086571</v>
+        <v>0.1022221222519875</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.002574211219325662</v>
+        <v>0.2477851659059525</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.0006808270700275898</v>
+        <v>0.03590391576290131</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001068280311301351</v>
+        <v>0.2039085775613785</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.008233994245529175</v>
+        <v>0.0149197094142437</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.008972295559942722</v>
+        <v>0.02063220553100109</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0008342977962456644</v>
+        <v>0.0785139799118042</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.003051071427762508</v>
+        <v>0.09902026504278183</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.001741949934512377</v>
+        <v>0.04727113991975784</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.001540759578347206</v>
+        <v>0.03589658066630363</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.002523801987990737</v>
+        <v>0.0145137682557106</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0009712696773931384</v>
+        <v>0.01050497591495514</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.003914644476026297</v>
+        <v>0.02047032862901688</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0004152602341491729</v>
+        <v>0.04253708943724632</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.001759147387929261</v>
+        <v>0.09080200642347336</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.00172768859192729</v>
+        <v>0.01292670145630836</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.001495817909017205</v>
+        <v>0.01726143062114716</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.000392443296732381</v>
+        <v>0.09289228171110153</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0009419170091859996</v>
+        <v>0.004030521027743816</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.001476528472267091</v>
+        <v>0.04541736096143723</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.00124642881564796</v>
+        <v>0.1024153828620911</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001058856141753495</v>
+        <v>0.005329832434654236</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.005374090280383825</v>
+        <v>0.1052201017737389</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0007155067287385464</v>
+        <v>0.05942484736442566</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.00337681220844388</v>
+        <v>0.009513719007372856</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.002490571467205882</v>
+        <v>0.07383778691291809</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.001736027537845075</v>
+        <v>0.02738378569483757</v>
       </c>
       <c r="EG5" t="n">
-        <v>7.315236143767834e-05</v>
+        <v>0.03494498133659363</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.002308588474988937</v>
+        <v>0.04904132708907127</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.003178675659000874</v>
+        <v>0.007612049579620361</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0009842318249866366</v>
+        <v>0.1175006702542305</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0007991641759872437</v>
+        <v>0.03020292520523071</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.001256013638339937</v>
+        <v>0.0102013498544693</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001997646177187562</v>
+        <v>0.03411407023668289</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.002818765351548791</v>
+        <v>0.02098736166954041</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001757323043420911</v>
+        <v>0.0007799791637808084</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0001445430680178106</v>
+        <v>0.09504292905330658</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.002306522335857153</v>
+        <v>0.0156627856194973</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.001494530588388443</v>
+        <v>0.03183962032198906</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0007419649627991021</v>
+        <v>0.07858376204967499</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.001319774193689227</v>
+        <v>0.0605153776705265</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.001103530172258615</v>
+        <v>0.02642750553786755</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.006214048247784376</v>
+        <v>0.08774743229150772</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001991725992411375</v>
+        <v>0.005394894629716873</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001452627824619412</v>
+        <v>0.025563919916749</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.001592902699485421</v>
+        <v>0.02637328207492828</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.00154184503480792</v>
+        <v>0.07091537863016129</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.001866506529040635</v>
+        <v>0.02041864395141602</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0005422310205176473</v>
+        <v>0.06703411042690277</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.001184811932034791</v>
+        <v>0.02949468232691288</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0008188174688257277</v>
+        <v>0.02066509425640106</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.00116415461525321</v>
+        <v>0.04048299789428711</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.002534416504204273</v>
+        <v>0.02355585992336273</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0001131428289227188</v>
+        <v>0.01824129745364189</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.001397060579620302</v>
+        <v>0.005685672629624605</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0006015376420691609</v>
+        <v>0.1334319114685059</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.003874579211696982</v>
+        <v>0.001921732909977436</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001191784162074327</v>
+        <v>0.1011789888143539</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.002019021427258849</v>
+        <v>0.08622961491346359</v>
       </c>
       <c r="FM5" t="n">
-        <v>6.285299605224282e-05</v>
+        <v>0.007216212339699268</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0006316401995718479</v>
+        <v>0.05154727026820183</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.003259875345975161</v>
+        <v>0.06428364664316177</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.004157811403274536</v>
+        <v>0.1446838676929474</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.004166671074926853</v>
+        <v>0.04339732974767685</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.007998150773346424</v>
+        <v>0.0431157685816288</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.003353392239660025</v>
+        <v>0.03463040292263031</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0009416175307705998</v>
+        <v>0.09032587707042694</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.004723747260868549</v>
+        <v>0.06351861357688904</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0006176097085699439</v>
+        <v>0.0513673722743988</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0005001265089958906</v>
+        <v>0.1378164738416672</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.003077492583543062</v>
+        <v>0.0390949547290802</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.001457139616832137</v>
+        <v>0.03086551651358604</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.001712103839963675</v>
+        <v>0.05555478855967522</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.002562878886237741</v>
+        <v>0.09039568156003952</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.003095895750448108</v>
+        <v>0.03581871092319489</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.005141093861311674</v>
+        <v>0.1383726596832275</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.004353445954620838</v>
+        <v>0.04699437320232391</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0007608864107169211</v>
+        <v>0.06045430898666382</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.002503447700291872</v>
+        <v>0.04730675742030144</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.001350847538560629</v>
+        <v>0.008830597624182701</v>
       </c>
     </row>
     <row r="6">
@@ -3844,5123 +3844,5123 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0002305226516909897</v>
+        <v>5.491178853844758e-07</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02591975033283234</v>
+        <v>2.923011197708547e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002964208135381341</v>
+        <v>1.169788356492063e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01103102043271065</v>
+        <v>5.552346465265146e-06</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007654672488570213</v>
+        <v>9.785577276488766e-06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01059658825397491</v>
+        <v>5.001332829124294e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>5.991174839437008e-05</v>
+        <v>4.60745195596246e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0004011260461993515</v>
+        <v>2.212188155681361e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003517847042530775</v>
+        <v>2.095171112159733e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002481943927705288</v>
+        <v>1.809492459869944e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02020467817783356</v>
+        <v>4.038347105961293e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004763688193634152</v>
+        <v>1.330785289610503e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>0.009984005242586136</v>
+        <v>9.470931217947509e-06</v>
       </c>
       <c r="N7" t="n">
-        <v>0.005820697639137506</v>
+        <v>8.489570973324589e-06</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0115693137049675</v>
+        <v>5.203789987717755e-05</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0006247751880437136</v>
+        <v>2.588622919574846e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003818530589342117</v>
+        <v>7.894976079114713e-06</v>
       </c>
       <c r="R7" t="n">
-        <v>0.002875155536457896</v>
+        <v>2.499224501661956e-05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000512082944624126</v>
+        <v>4.42680720880162e-06</v>
       </c>
       <c r="T7" t="n">
-        <v>0.003484508721157908</v>
+        <v>1.189944214274874e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>3.18642778438516e-05</v>
+        <v>1.739203071338125e-06</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003992524463683367</v>
+        <v>1.030399744195165e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.000981654622592032</v>
+        <v>6.646562724199612e-06</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004292549565434456</v>
+        <v>1.110296125261812e-05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001084394403733313</v>
+        <v>3.930074399249861e-06</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002377431374043226</v>
+        <v>2.593125145722297e-07</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0006237121415324509</v>
+        <v>7.254709998960607e-06</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001133088837377727</v>
+        <v>4.297990017221309e-06</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003494084347039461</v>
+        <v>1.600831456016749e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0001294114335905761</v>
+        <v>1.44964833452832e-05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001059632981196046</v>
+        <v>1.055081884260289e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001896170433610678</v>
+        <v>1.460014209442306e-05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.002392061986029148</v>
+        <v>1.177785270556342e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0001919904025271535</v>
+        <v>1.013392989079875e-06</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.001529967645183206</v>
+        <v>2.628416223160457e-05</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001687875483185053</v>
+        <v>2.595983914943645e-06</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.00414492329582572</v>
+        <v>2.445485051794094e-06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.002921930979937315</v>
+        <v>8.407585482927971e-06</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0005599282449111342</v>
+        <v>8.99581573321484e-06</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.001985823269933462</v>
+        <v>3.914966782758711e-06</v>
       </c>
       <c r="AO7" t="n">
-        <v>9.716231579659507e-05</v>
+        <v>1.499407744631753e-07</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.002262579975649714</v>
+        <v>9.920137017616071e-06</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0009758750675246119</v>
+        <v>3.909007318725344e-06</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.00176558957900852</v>
+        <v>7.279146757355193e-06</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.002155072055757046</v>
+        <v>3.491154984658351e-06</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.001722238725051284</v>
+        <v>2.588785719126463e-07</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.01962291821837425</v>
+        <v>3.641773946583271e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.001283221645280719</v>
+        <v>1.67944763234118e-05</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.002489314647391438</v>
+        <v>2.786042387015186e-06</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.001526581821963191</v>
+        <v>1.334844273515046e-05</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.003507186658680439</v>
+        <v>3.583121360861696e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.003544511506333947</v>
+        <v>2.901344942074502e-06</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.001344577292911708</v>
+        <v>2.212325625805533e-06</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001337859896011651</v>
+        <v>2.754772140178829e-06</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0006824795855209231</v>
+        <v>8.870755436873878e-07</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.007715879008173943</v>
+        <v>2.162926466553472e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.006105320993810892</v>
+        <v>6.027266863384284e-06</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001528706983663142</v>
+        <v>1.285777216253337e-06</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.008416094817221165</v>
+        <v>7.989438017830253e-06</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.006590681150555611</v>
+        <v>1.1745164556487e-06</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.002593263285234571</v>
+        <v>2.801489245030098e-06</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.00587500398978591</v>
+        <v>1.394200808135793e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.003528423141688108</v>
+        <v>2.555354967626045e-07</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.003397752065211535</v>
+        <v>5.213923486735439e-06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.006745063234120607</v>
+        <v>1.250017976417439e-05</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.002706324914470315</v>
+        <v>4.359673312137602e-06</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0002111001231241971</v>
+        <v>2.301001131854719e-07</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.002674374729394913</v>
+        <v>8.327760042448062e-06</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.002090086927637458</v>
+        <v>1.630854058021214e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0007188342278823256</v>
+        <v>1.108047399611678e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0009678379283286631</v>
+        <v>5.2697682804137e-06</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.000666483654640615</v>
+        <v>7.765705959172919e-06</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.001801370410248637</v>
+        <v>1.664505759890744e-07</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01037179958075285</v>
+        <v>2.161910379072651e-05</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.003848119871690869</v>
+        <v>7.369065315288026e-06</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.003100050846114755</v>
+        <v>1.192191393784015e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0003753661003429443</v>
+        <v>5.288070497044828e-06</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.001479137688875198</v>
+        <v>2.083213439618703e-05</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.158439934253693e-05</v>
+        <v>4.335659014031989e-06</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.000318586069624871</v>
+        <v>1.254896051250398e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.001289917854592204</v>
+        <v>7.304424798348919e-07</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0005126291653141379</v>
+        <v>1.807649823604152e-06</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.003597656032070518</v>
+        <v>8.959813385445159e-06</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.001819856464862823</v>
+        <v>7.619909183631535e-07</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0008356707403436303</v>
+        <v>4.53294478575117e-06</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0006827133474871516</v>
+        <v>3.433261781538022e-06</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001851171371527016</v>
+        <v>9.964545824914239e-06</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001335377455689013</v>
+        <v>9.136478524851555e-07</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0008071984630078077</v>
+        <v>7.09448431734927e-06</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0007667681202292442</v>
+        <v>1.781948981260939e-06</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.004750375635921955</v>
+        <v>7.491967608075356e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.00450605945661664</v>
+        <v>5.31839941686485e-06</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0009388506878167391</v>
+        <v>1.565615821164101e-05</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.004913191311061382</v>
+        <v>5.114086434332421e-07</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.002690080320462584</v>
+        <v>5.525816504814429e-06</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0006899146246723831</v>
+        <v>5.600895747193135e-09</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.003405640367418528</v>
+        <v>2.610828232718632e-06</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.003404007758945227</v>
+        <v>6.536663477163529e-07</v>
       </c>
       <c r="CU7" t="n">
-        <v>9.099887392949313e-05</v>
+        <v>2.047212910838425e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>6.558626773767173e-05</v>
+        <v>4.110161171411164e-06</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.002744009252637625</v>
+        <v>6.813264008087572e-06</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.002449752762913704</v>
+        <v>1.923193394759437e-06</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.001929632504470646</v>
+        <v>3.276560619269731e-06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0003874437825288624</v>
+        <v>8.698926876604673e-07</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.002244707196950912</v>
+        <v>1.169067763839848e-05</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0008806592668406665</v>
+        <v>1.631737291063473e-06</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.001207828754559159</v>
+        <v>6.36599224890233e-06</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.00030460802372545</v>
+        <v>8.020644486350648e-07</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001680861110799015</v>
+        <v>6.628718438150827e-06</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.002896798308938742</v>
+        <v>9.375818990520202e-06</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.001603025826625526</v>
+        <v>8.14473423815798e-06</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.007152703125029802</v>
+        <v>3.982355792686576e-06</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.002826693467795849</v>
+        <v>4.499395799939521e-06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.001436923164874315</v>
+        <v>8.071408046816941e-06</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.004256211686879396</v>
+        <v>3.113050070169265e-06</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0003817597171291709</v>
+        <v>5.698981112800539e-06</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.004896678496152163</v>
+        <v>3.404416247576592e-06</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0005639145383611321</v>
+        <v>6.901273536641384e-06</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0009683734970167279</v>
+        <v>3.166583610436646e-06</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.002298608887940645</v>
+        <v>4.533009814622346e-06</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0006350595504045486</v>
+        <v>1.287299346586224e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0001818893069867045</v>
+        <v>3.479982751741773e-06</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0009890539804473519</v>
+        <v>6.557398592121899e-06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.001452216180041432</v>
+        <v>8.957942554843612e-06</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.001329857273958623</v>
+        <v>1.130876853494556e-06</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.001376645173877478</v>
+        <v>9.218677405442577e-06</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0002109005290549248</v>
+        <v>6.279971785261296e-06</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.172720269300044e-05</v>
+        <v>5.148456693859771e-06</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.003061129245907068</v>
+        <v>1.462886211811565e-05</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.002462179632857442</v>
+        <v>8.638492658974428e-07</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001519001321867108</v>
+        <v>8.400596016144846e-06</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.000837286002933979</v>
+        <v>1.426448761776555e-05</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0001867151877377182</v>
+        <v>2.320426801816211e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.001080015557818115</v>
+        <v>1.725566107779741e-07</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0001221637648995966</v>
+        <v>9.514749763184227e-06</v>
       </c>
       <c r="EF7" t="n">
-        <v>3.447302151471376e-05</v>
+        <v>2.179574266847339e-06</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.002298825886100531</v>
+        <v>1.140318431680498e-06</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0005543503211811185</v>
+        <v>7.01281624060357e-06</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0002143732272088528</v>
+        <v>2.071985818474786e-07</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0003993004793301225</v>
+        <v>3.636357178038452e-06</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.001739312312565744</v>
+        <v>5.657406290993094e-06</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.001777115510776639</v>
+        <v>1.266080744244391e-06</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.001048268866725266</v>
+        <v>8.400132173846941e-06</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0004304421017877758</v>
+        <v>2.182333219025168e-06</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0009145438671112061</v>
+        <v>1.602164729774813e-06</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0002174805558752269</v>
+        <v>3.671087142720353e-06</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.002246755175292492</v>
+        <v>7.250010639836546e-06</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0009500464075244963</v>
+        <v>8.867100405041128e-07</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0009768323507159948</v>
+        <v>9.956043868442066e-06</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.004414538852870464</v>
+        <v>1.110612811316969e-05</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.001123025896959007</v>
+        <v>5.397031600296032e-06</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.005336962174624205</v>
+        <v>4.73436011816375e-06</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.00166522164363414</v>
+        <v>2.131259407178732e-06</v>
       </c>
       <c r="EX7" t="n">
-        <v>1.697090920060873e-05</v>
+        <v>4.480547431739978e-06</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.002417345996946096</v>
+        <v>1.069332483893959e-05</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.001373340026475489</v>
+        <v>2.396361878709286e-06</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.001242064172402024</v>
+        <v>3.213203399354825e-06</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0006948152440600097</v>
+        <v>2.788633992167888e-06</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.002206109929829836</v>
+        <v>8.764456651988439e-06</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.001527392887510359</v>
+        <v>1.577250600348634e-06</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0005291773704811931</v>
+        <v>4.141986210015602e-06</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.00107487675268203</v>
+        <v>3.099652531091124e-06</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0008736710879020393</v>
+        <v>6.199359631864354e-06</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.002253334270790219</v>
+        <v>7.292365808098111e-06</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.00181154441088438</v>
+        <v>1.782561412255745e-05</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.005342365242540836</v>
+        <v>3.37895585289516e-06</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.002177741145715117</v>
+        <v>1.783432708180044e-07</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0008171203080564737</v>
+        <v>6.138792741694488e-06</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.001626315526664257</v>
+        <v>2.361684664720087e-06</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.001605382072739303</v>
+        <v>7.826904948160518e-06</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0005224051419645548</v>
+        <v>1.630531733098906e-05</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.00144912744872272</v>
+        <v>7.612851277372101e-06</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.007958345115184784</v>
+        <v>1.989369775401428e-05</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.0001769606315065175</v>
+        <v>1.513806455477607e-05</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.004264445975422859</v>
+        <v>9.01743806025479e-06</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.00442289374768734</v>
+        <v>9.774850695976056e-06</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.002393146743997931</v>
+        <v>1.293555033043958e-05</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.005945638287812471</v>
+        <v>9.689674698165618e-06</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.001693196129053831</v>
+        <v>1.751409581629559e-05</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.002198722679167986</v>
+        <v>1.761778548825532e-05</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.003157841041684151</v>
+        <v>3.971370006183861e-07</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.001139731728471816</v>
+        <v>1.915347183967242e-06</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.001243138452991843</v>
+        <v>8.316163075505756e-06</v>
       </c>
       <c r="GB7" t="n">
-        <v>7.077452028170228e-05</v>
+        <v>1.763274667609949e-06</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0006037211278453469</v>
+        <v>2.504363510524854e-05</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.002839240478351712</v>
+        <v>1.859090662037488e-05</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.00776763679459691</v>
+        <v>4.480839947973436e-07</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.002180211944505572</v>
+        <v>5.787778718513437e-07</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.0003963765338994563</v>
+        <v>1.315621716457827e-06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.002000725595280528</v>
+        <v>0.002120454795658588</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04919452220201492</v>
+        <v>0.01032302714884281</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004234264604747295</v>
+        <v>0.000956724165007472</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02677931264042854</v>
+        <v>0.003181282430887222</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00499558774754405</v>
+        <v>0.002820479683578014</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005032177083194256</v>
+        <v>0.001317203976213932</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005122170317918062</v>
+        <v>0.002347381319850683</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002348866546526551</v>
+        <v>0.001510699046775699</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002524204785004258</v>
+        <v>0.0002548455959185958</v>
       </c>
       <c r="J8" t="n">
-        <v>0.007250350899994373</v>
+        <v>0.0007484710076823831</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03900377824902534</v>
+        <v>0.01067674346268177</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003175024874508381</v>
+        <v>0.001252890098839998</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02515428699553013</v>
+        <v>0.005642888136208057</v>
       </c>
       <c r="N8" t="n">
-        <v>0.006949150934815407</v>
+        <v>0.004790377337485552</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006400128826498985</v>
+        <v>0.001097442116588354</v>
       </c>
       <c r="P8" t="n">
-        <v>0.003383883973583579</v>
+        <v>0.001977537292987108</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005286268424242735</v>
+        <v>0.0005801839870400727</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003237666329368949</v>
+        <v>0.001215406460687518</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001771731767803431</v>
+        <v>0.0003570809494704008</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007612388115376234</v>
+        <v>0.001037282636389136</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0007964872638694942</v>
+        <v>0.0009728196891956031</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003717465326189995</v>
+        <v>0.00108179310336709</v>
       </c>
       <c r="W8" t="n">
-        <v>2.914073411375284e-05</v>
+        <v>0.0007555960910394788</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003985132556408644</v>
+        <v>0.0006411258364096284</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005290789064019918</v>
+        <v>0.0006013443926349282</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004468716215342283</v>
+        <v>0.0004447603423614055</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.003908767830580473</v>
+        <v>0.002096859272569418</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.005429981276392937</v>
+        <v>0.00173805037047714</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.004918498452752829</v>
+        <v>0.0008498848183080554</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.001378222834318876</v>
+        <v>0.0009010059293359518</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002433347748592496</v>
+        <v>0.001767409732565284</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001518549048341811</v>
+        <v>0.002845730632543564</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001536541851237416</v>
+        <v>0.002491478575393558</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.002891777083277702</v>
+        <v>0.0009293557959608734</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0005698084132745862</v>
+        <v>0.001226291875354946</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002329850802198052</v>
+        <v>0.0006460007862187922</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.003013553563505411</v>
+        <v>0.0001243275473825634</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.006947053130716085</v>
+        <v>0.002236685482785106</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.000644580228254199</v>
+        <v>0.0005506394081749022</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001396955805830657</v>
+        <v>0.000762623269110918</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.000634140451438725</v>
+        <v>0.0005549126071855426</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.002713919384405017</v>
+        <v>0.0006356857484206557</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002128170104697347</v>
+        <v>0.0001060778158716857</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.003044873476028442</v>
+        <v>0.0003658684436231852</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.002790910424664617</v>
+        <v>3.277079667896032e-05</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.00439919251948595</v>
+        <v>0.0009327302686870098</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.03131752461194992</v>
+        <v>0.005637113004922867</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0009077697759494185</v>
+        <v>9.5334806246683e-05</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.007740217726677656</v>
+        <v>0.001133663696236908</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0004749720683321357</v>
+        <v>0.004923526663333178</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002046076580882072</v>
+        <v>0.0003356177185196429</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.00123137142509222</v>
+        <v>0.0003288458101451397</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001770442584529519</v>
+        <v>0.001023335615172982</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.003691257443279028</v>
+        <v>0.0005238193552941084</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.001366275595501065</v>
+        <v>0.0005404519033618271</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.009072870947420597</v>
+        <v>0.0003500870079733431</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0074206767603755</v>
+        <v>0.00157232501078397</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.004243963863700628</v>
+        <v>0.001996977021917701</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0123095540329814</v>
+        <v>0.0008620989974588156</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.002302538370713592</v>
+        <v>0.0009429473429918289</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005634299013763666</v>
+        <v>0.000758187030442059</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.004597354214638472</v>
+        <v>0.001387777738273144</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001646205550059676</v>
+        <v>0.0001394742866978049</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.006644865032285452</v>
+        <v>0.0001171467010863125</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001125284121371806</v>
+        <v>0.0001113221806008369</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0008583067683503032</v>
+        <v>0.0001867025712272152</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0002881232067011297</v>
+        <v>0.0003304903220850974</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0009263696847483516</v>
+        <v>0.001431482029147446</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.003795306663960218</v>
+        <v>4.368949885247275e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0002478612295817584</v>
+        <v>0.0007075166795402765</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001282956684008241</v>
+        <v>0.00011209739750484</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001893924083560705</v>
+        <v>0.0004900096682831645</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.004821078851819038</v>
+        <v>0.0001545075210742652</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.01756571047008038</v>
+        <v>0.00475213211029768</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.003208546666428447</v>
+        <v>6.84030819684267e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.006986770778894424</v>
+        <v>0.001096373307518661</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.002668232657015324</v>
+        <v>0.001258321106433868</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001446028938516974</v>
+        <v>0.001086911535821855</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.002470499603077769</v>
+        <v>0.00133285706397146</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001917541376315057</v>
+        <v>0.0007319874130189419</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.003567748935893178</v>
+        <v>0.001624800032004714</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.001899268012493849</v>
+        <v>6.645507528446615e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.006935962475836277</v>
+        <v>0.002987915650010109</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.002444121753796935</v>
+        <v>0.0004649441107176244</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003349059959873557</v>
+        <v>0.001250551082193851</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.002238468267023563</v>
+        <v>0.0003067524521611631</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001707536750473082</v>
+        <v>0.0006200661882758141</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.00156904780305922</v>
+        <v>0.0002132272638846189</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0005554604576900601</v>
+        <v>4.35268520959653e-06</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.001943090348504484</v>
+        <v>0.0001796036085579544</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.007794519420713186</v>
+        <v>0.001023086020722985</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001343509880825877</v>
+        <v>0.001907663885504007</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0004882487410213798</v>
+        <v>0.002170150401070714</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.006005109753459692</v>
+        <v>0.004706544801592827</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.003926186356693506</v>
+        <v>0.001886010053567588</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.00276088947430253</v>
+        <v>0.002013382036238909</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.004386868327856064</v>
+        <v>0.0004514848114922643</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.005203157663345337</v>
+        <v>0.0006832819781266153</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.001466615940444171</v>
+        <v>0.0007227763999253511</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0009522681357339025</v>
+        <v>0.0001910665014293045</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.007195484824478626</v>
+        <v>0.00286416825838387</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.002949450630694628</v>
+        <v>0.0004726598272100091</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.004587253555655479</v>
+        <v>0.001286071492359042</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002109887544065714</v>
+        <v>0.0008114867378026247</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.002403771271929145</v>
+        <v>0.0006807218305766582</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.001455234130844474</v>
+        <v>0.0001853870926424861</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.001350851729512215</v>
+        <v>0.0001274125243071467</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0009406751487404108</v>
+        <v>0.0005024868296459317</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.002669423585757613</v>
+        <v>0.001159236999228597</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.007481983397156</v>
+        <v>0.002297753700986505</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0006076463032513857</v>
+        <v>0.0004050240677315742</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.01283627096563578</v>
+        <v>0.001637688721530139</v>
       </c>
       <c r="DI8" t="n">
-        <v>3.636180190369487e-05</v>
+        <v>0.001905524986796081</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.002012860029935837</v>
+        <v>0.003302590688690543</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.004161264281719923</v>
+        <v>0.001042456249706447</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.00026441685622558</v>
+        <v>0.000875666388310492</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002275498700328171</v>
+        <v>0.001404877984896302</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.002287356182932854</v>
+        <v>0.0004066177643835545</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001075438805855811</v>
+        <v>0.001998665742576122</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.002802297240123153</v>
+        <v>0.000558409548830241</v>
       </c>
       <c r="DQ8" t="n">
-        <v>7.185405411291867e-05</v>
+        <v>0.0006407508626580238</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.005813125986605883</v>
+        <v>0.0005427928408607841</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.005629499442875385</v>
+        <v>0.0004852672864217311</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.000796753796748817</v>
+        <v>0.0001153181656263769</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.002211227314546704</v>
+        <v>8.002622053027153e-06</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.003536834847182035</v>
+        <v>0.00205276976339519</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0009551700786687434</v>
+        <v>0.0007862208294682205</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.001444340567104518</v>
+        <v>0.0004787794314324856</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.004016670398414135</v>
+        <v>0.0006721941754221916</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.003667176235467196</v>
+        <v>0.001241063582710922</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.003839637851342559</v>
+        <v>0.0009734489722177386</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0004207643214613199</v>
+        <v>0.002151165623217821</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.001840493525378406</v>
+        <v>6.522407056763768e-05</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.001427902840077877</v>
+        <v>0.001604667399078608</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.001584479119628668</v>
+        <v>0.001903654308989644</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0003646934637799859</v>
+        <v>0.001102410373277962</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.005229957867413759</v>
+        <v>0.00228265393525362</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.002946158405393362</v>
+        <v>0.0006951061077415943</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.00277290865778923</v>
+        <v>0.00110593787394464</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.002279456006363034</v>
+        <v>8.577898552175611e-05</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.004782558418810368</v>
+        <v>5.361007060855627e-05</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.001464216620661318</v>
+        <v>0.00037669442826882</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0005272967973724008</v>
+        <v>0.0003415087121538818</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.000770365702919662</v>
+        <v>0.0002379479556111619</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0001447953982278705</v>
+        <v>0.0003060486051253974</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.005699532572180033</v>
+        <v>0.002584275556728244</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.004744760226458311</v>
+        <v>0.0006172338034957647</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.00170671462547034</v>
+        <v>0.001003078185021877</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.001773892086930573</v>
+        <v>0.0008794021559879184</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.007020140998065472</v>
+        <v>0.001087681390345097</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.003793716197833419</v>
+        <v>0.0007023104699328542</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.004312335979193449</v>
+        <v>4.2452295019757e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0005052594933658838</v>
+        <v>0.001142824767157435</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0001745438203215599</v>
+        <v>0.0002307480899617076</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.007586750201880932</v>
+        <v>0.003349924460053444</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.001467097899876535</v>
+        <v>0.000328294700011611</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.004215617664158344</v>
+        <v>0.00162302574608475</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.00226190872490406</v>
+        <v>0.0004156247014179826</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.002569385338574648</v>
+        <v>0.0006836992688477039</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.002320849103853106</v>
+        <v>0.0001819922326831147</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0006447762716561556</v>
+        <v>9.792200580704957e-05</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.001888980623334646</v>
+        <v>0.0005077607347629964</v>
       </c>
       <c r="FG8" t="n">
-        <v>0.0005175230908207595</v>
+        <v>0.0004102930834051222</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.005061819683760405</v>
+        <v>0.0008867348660714924</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.001149943447671831</v>
+        <v>0.0008584419265389442</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.004566723946481943</v>
+        <v>0.0004511374863795936</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.003066473873332143</v>
+        <v>0.000155060799443163</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.001808207714930177</v>
+        <v>0.00106079108081758</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.000766958633903414</v>
+        <v>0.0001547276915516704</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.00157778081484139</v>
+        <v>0.0002810905571095645</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.001848100800998509</v>
+        <v>0.000373101094737649</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.00111759826540947</v>
+        <v>0.0002300762134836987</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.00893778633326292</v>
+        <v>0.0003999753389507532</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.005628736224025488</v>
+        <v>9.26025677472353e-05</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.00428833207115531</v>
+        <v>0.001245758961886168</v>
       </c>
       <c r="FT8" t="n">
-        <v>8.862081449478865e-05</v>
+        <v>0.001831857254728675</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0001069401478162035</v>
+        <v>0.001173685071989894</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0005431452300399542</v>
+        <v>0.001380019588395953</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0003408840857446194</v>
+        <v>0.000462180410977453</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.002472540363669395</v>
+        <v>0.001614421373233199</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.005826880224049091</v>
+        <v>0.001300383359193802</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.001520252088084817</v>
+        <v>0.002146367449313402</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0003470866358838975</v>
+        <v>0.0005251270486041903</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0005025948630645871</v>
+        <v>0.001203593099489808</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.004655671771615744</v>
+        <v>0.002094936091452837</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.003761880565434694</v>
+        <v>0.0007197750965133309</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.01334268692880869</v>
+        <v>0.0008231409592553973</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.001965942094102502</v>
+        <v>0.0001106607232941315</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.002641458762809634</v>
+        <v>0.0008543711737729609</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.002570009790360928</v>
+        <v>0.09911325573921204</v>
       </c>
       <c r="B9" t="n">
-        <v>0.03030559979379177</v>
+        <v>0.3199740648269653</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001856266404502094</v>
+        <v>0.03092695027589798</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0141471903771162</v>
+        <v>0.04048930108547211</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005802799016237259</v>
+        <v>0.08093731850385666</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01856832951307297</v>
+        <v>0.01465108618140221</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002480364637449384</v>
+        <v>0.03936374932527542</v>
       </c>
       <c r="H9" t="n">
-        <v>0.008455804549157619</v>
+        <v>0.02770483121275902</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00204548891633749</v>
+        <v>0.04355321452021599</v>
       </c>
       <c r="J9" t="n">
-        <v>0.006684280931949615</v>
+        <v>0.08977852761745453</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02421852573752403</v>
+        <v>0.3975005745887756</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0006107030785642564</v>
+        <v>0.01572372764348984</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01228618435561657</v>
+        <v>0.1336891055107117</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004272749647498131</v>
+        <v>0.1080447882413864</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01975871995091438</v>
+        <v>0.08092804998159409</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00091352011077106</v>
+        <v>0.01054018177092075</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.001375171006657183</v>
+        <v>0.02257773466408253</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002222781535238028</v>
+        <v>0.07794348895549774</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002324643544852734</v>
+        <v>0.01555069163441658</v>
       </c>
       <c r="T9" t="n">
-        <v>0.004974126350134611</v>
+        <v>0.03657425194978714</v>
       </c>
       <c r="U9" t="n">
-        <v>0.001367994351312518</v>
+        <v>0.00739671103656292</v>
       </c>
       <c r="V9" t="n">
-        <v>0.002033147029578686</v>
+        <v>0.00814506970345974</v>
       </c>
       <c r="W9" t="n">
-        <v>0.001476934063248336</v>
+        <v>0.01059356331825256</v>
       </c>
       <c r="X9" t="n">
-        <v>0.002958001801744103</v>
+        <v>0.007556161377578974</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.003167935414239764</v>
+        <v>0.02293051034212112</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.002420217264443636</v>
+        <v>0.02648370899260044</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.003497333964332938</v>
+        <v>0.03455394878983498</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0002905880101025105</v>
+        <v>0.01418741978704929</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.003423130372539163</v>
+        <v>0.02573474496603012</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.000884783046785742</v>
+        <v>0.01881292462348938</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0003011600056197494</v>
+        <v>0.03626649081707001</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0008915277430787683</v>
+        <v>0.04556506872177124</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0005269481334835291</v>
+        <v>0.05449499189853668</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001201806589961052</v>
+        <v>0.01007390208542347</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001748816343024373</v>
+        <v>0.07792345434427261</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.001392648089677095</v>
+        <v>0.04322877898812294</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.003077439032495022</v>
+        <v>0.001163673121482134</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.005078394897282124</v>
+        <v>0.05184102803468704</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001714032143354416</v>
+        <v>0.02723251655697823</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.0001103724353015423</v>
+        <v>0.003129646182060242</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001295947236940265</v>
+        <v>0.004393310286104679</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.003571874462068081</v>
+        <v>0.02838502824306488</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0002567244227975607</v>
+        <v>0.02257651463150978</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.002631524112075567</v>
+        <v>0.03443515673279762</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.003479937091469765</v>
+        <v>0.02842716872692108</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001958727603778243</v>
+        <v>0.04470888525247574</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01904307305812836</v>
+        <v>0.2567625045776367</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.000969036715105176</v>
+        <v>0.03111990541219711</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001669409684836864</v>
+        <v>0.00958313699811697</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001658741384744644</v>
+        <v>0.09006784856319427</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01013669185340405</v>
+        <v>0.04915595799684525</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0007285173633135855</v>
+        <v>0.006577001418918371</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.004540163557976484</v>
+        <v>0.01000125519931316</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.005167839583009481</v>
+        <v>0.01568427309393883</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.002232047263532877</v>
+        <v>0.03418977558612823</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.005256694741547108</v>
+        <v>0.01149049960076809</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.00701706251129508</v>
+        <v>0.04332566261291504</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002822049427777529</v>
+        <v>0.01489661447703838</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.008345764130353928</v>
+        <v>0.04160396009683609</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.003902360564097762</v>
+        <v>0.02541597932577133</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001032209489494562</v>
+        <v>0.03575082868337631</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.004580094013363123</v>
+        <v>0.02171154692769051</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0009519890882074833</v>
+        <v>0.04082790017127991</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0001772297546267509</v>
+        <v>0.009061010554432869</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002867842558771372</v>
+        <v>0.01712559163570404</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.002517201472073793</v>
+        <v>0.004765953868627548</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.002907036105170846</v>
+        <v>0.04351398348808289</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0001412501296726987</v>
+        <v>0.04888328909873962</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.001009199535474181</v>
+        <v>0.002179118804633617</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.001404659473337233</v>
+        <v>0.0277833566069603</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0002632112009450793</v>
+        <v>0.02769077941775322</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.00213338783942163</v>
+        <v>0.002455516718327999</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.002069550799205899</v>
+        <v>0.002335095778107643</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.009887568652629852</v>
+        <v>0.1835799515247345</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.003068771911785007</v>
+        <v>0.0125752380117774</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.003215515520423651</v>
+        <v>0.04065179079771042</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.001992829144001007</v>
+        <v>0.01593475416302681</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.002939159981906414</v>
+        <v>0.01049240306019783</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.001207729568704963</v>
+        <v>0.0293906033039093</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002524952171370387</v>
+        <v>0.0008884817361831665</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.004290793091058731</v>
+        <v>0.00462706945836544</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0008611426455900073</v>
+        <v>0.02612378820776939</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.004733387846499681</v>
+        <v>0.1000864505767822</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.003236833494156599</v>
+        <v>0.01224566996097565</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002462973818182945</v>
+        <v>0.0186892207711935</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001508660498075187</v>
+        <v>0.01807321049273014</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.003248493187129498</v>
+        <v>0.008837301284074783</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.001798459095880389</v>
+        <v>0.00215714517980814</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001183520071208477</v>
+        <v>0.0147197674959898</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.002080226317048073</v>
+        <v>0.007742407731711864</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.003578889649361372</v>
+        <v>0.01332561671733856</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0004757258284371346</v>
+        <v>0.1552457064390182</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.001185274333693087</v>
+        <v>0.04712607711553574</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.003347714431583881</v>
+        <v>0.01090825628489256</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001581230433657765</v>
+        <v>0.03461851924657822</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.002129680477082729</v>
+        <v>0.04031061381101608</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.004914704710245132</v>
+        <v>0.002934294752776623</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.004172645509243011</v>
+        <v>0.01052354369312525</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0003848952474072576</v>
+        <v>0.0002396265044808388</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0002339605707675219</v>
+        <v>0.01543014962226152</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.004357451573014259</v>
+        <v>0.1036353260278702</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.003141781548038125</v>
+        <v>0.01129843294620514</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.003738034050911665</v>
+        <v>0.01826689019799232</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.00118546059820801</v>
+        <v>0.003678790526464581</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.003868651809170842</v>
+        <v>0.01015005726367235</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001698408741503954</v>
+        <v>0.01434393413364887</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.002777234185487032</v>
+        <v>0.01624390855431557</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.001041639246977866</v>
+        <v>0.02791441045701504</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.00244493642821908</v>
+        <v>0.07486103475093842</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.00426127202808857</v>
+        <v>0.04544374346733093</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0009652138687670231</v>
+        <v>0.002535394858568907</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.007247185800224543</v>
+        <v>0.03630658984184265</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0002750838757492602</v>
+        <v>0.015585632994771</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001721733016893268</v>
+        <v>0.1584372818470001</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.002746703568845987</v>
+        <v>0.006362549029290676</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.002819347195327282</v>
+        <v>0.009027641266584396</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0003386707685422152</v>
+        <v>0.02489401400089264</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.000761725939810276</v>
+        <v>0.01488893292844296</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0002066951856249943</v>
+        <v>0.03740765154361725</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001253649243153632</v>
+        <v>0.02528287284076214</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.002548067830502987</v>
+        <v>0.07482679933309555</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0002737458562478423</v>
+        <v>0.001663768198341131</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.001052819425240159</v>
+        <v>0.04888516291975975</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001422148430719972</v>
+        <v>0.0056145996786654</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.001160231186076999</v>
+        <v>0.06330548971891403</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.003993713762611151</v>
+        <v>0.01999795809388161</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.001054214779287577</v>
+        <v>0.01990310847759247</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001735443715006113</v>
+        <v>0.05647718161344528</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.005902024451643229</v>
+        <v>0.05196402221918106</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0005662616458721459</v>
+        <v>0.02592223882675171</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.001217915560118854</v>
+        <v>0.05498108640313148</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.001889114268124104</v>
+        <v>0.07123751193284988</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0004604244895745069</v>
+        <v>0.006754395086318254</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.002333675511181355</v>
+        <v>0.1259870380163193</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0007372885011136532</v>
+        <v>0.05800321698188782</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001735932659357786</v>
+        <v>0.04556077718734741</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.003062334610149264</v>
+        <v>0.04836542904376984</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.002233246807008982</v>
+        <v>0.005270637571811676</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0001264181628357619</v>
+        <v>0.08069255948066711</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0001606615260243416</v>
+        <v>0.01527216378599405</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.003665858646854758</v>
+        <v>0.004468562081456184</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.001971333054825664</v>
+        <v>0.004339729435741901</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0001576323993504047</v>
+        <v>0.0363934338092804</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0006188371917232871</v>
+        <v>0.01162596978247166</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.0005696727312169969</v>
+        <v>0.001513740979135036</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.002189045771956444</v>
+        <v>0.05651424825191498</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.003155430778861046</v>
+        <v>0.01019851677119732</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.001994834048673511</v>
+        <v>0.002202242612838745</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.003340501803904772</v>
+        <v>0.0471317358314991</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.005217219702899456</v>
+        <v>0.04303096607327461</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.003887758124619722</v>
+        <v>0.02907147258520126</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.006383049301803112</v>
+        <v>0.002541880123317242</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0009702060488052666</v>
+        <v>0.01669421419501305</v>
       </c>
       <c r="EX9" t="n">
-        <v>8.802482625469565e-05</v>
+        <v>0.01779079809784889</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.004196236375719309</v>
+        <v>0.1182695552706718</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.002173182554543018</v>
+        <v>0.009925452992320061</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.00299219973385334</v>
+        <v>0.02191154845058918</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.001987332012504339</v>
+        <v>0.007312630768865347</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.003130384953692555</v>
+        <v>0.01076203770935535</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.002728651510551572</v>
+        <v>0.001636388711631298</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.001787957036867738</v>
+        <v>0.01599802076816559</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.002102249534800649</v>
+        <v>0.02358867600560188</v>
       </c>
       <c r="FG9" t="n">
-        <v>3.911597013939172e-05</v>
+        <v>0.01213121321052313</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.002690651454031467</v>
+        <v>0.05563280358910561</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.003949364181607962</v>
+        <v>0.0564458854496479</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.004389201756566763</v>
+        <v>0.06877966970205307</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.000261927314568311</v>
+        <v>0.01067154109477997</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0009752654586918652</v>
+        <v>0.01036214549094439</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.000715685891918838</v>
+        <v>0.01995052769780159</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.002774131717160344</v>
+        <v>0.02760053239762783</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.002431914210319519</v>
+        <v>0.01204859837889671</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.000747540092561394</v>
+        <v>0.07664345949888229</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.007618875242769718</v>
+        <v>0.09415927529335022</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.002431559842079878</v>
+        <v>0.03600697219371796</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.003906232537701726</v>
+        <v>0.042149618268013</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.001658392138779163</v>
+        <v>0.07986172288656235</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.002407968742772937</v>
+        <v>0.001375551335513592</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.002849381882697344</v>
+        <v>0.05447237938642502</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.001830795546993613</v>
+        <v>0.01442430354654789</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0002414631308056414</v>
+        <v>0.04639406502246857</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.004439528100192547</v>
+        <v>0.02045619487762451</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.001036608591675758</v>
+        <v>0.04502462595701218</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.001714240177534521</v>
+        <v>0.01126821339130402</v>
       </c>
       <c r="GB9" t="n">
-        <v>6.462544115493074e-05</v>
+        <v>0.06143836677074432</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.006709784734994173</v>
+        <v>0.04730333387851715</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.002878275234252214</v>
+        <v>0.0113081531599164</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.01389204058796167</v>
+        <v>0.005324350669980049</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.0009490991942584515</v>
+        <v>0.04302730783820152</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.00193269900046289</v>
+        <v>0.04464049264788628</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.001700326567515731</v>
+        <v>2.831129393143783e-07</v>
       </c>
       <c r="B10" t="n">
-        <v>0.007427787873893976</v>
+        <v>1.144494035543175e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0006777484668418765</v>
+        <v>2.462667225699988e-07</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004780346993356943</v>
+        <v>4.523516849985754e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>0.000991511158645153</v>
+        <v>5.322195306689537e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001449442468583584</v>
+        <v>4.280879295492923e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>0.000458496535429731</v>
+        <v>6.546726183387364e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>8.771946158958599e-05</v>
+        <v>1.564534386488958e-07</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0005285241641104221</v>
+        <v>1.448156865535566e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002295357408002019</v>
+        <v>1.339463722160872e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>0.005197742022573948</v>
+        <v>1.475171075071557e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00065421691397205</v>
+        <v>2.493159740879491e-07</v>
       </c>
       <c r="M10" t="n">
-        <v>0.003514377865940332</v>
+        <v>2.900632694036176e-07</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001430485513992608</v>
+        <v>6.923584692231088e-07</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002568589989095926</v>
+        <v>1.433245984117093e-07</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0008460800163447857</v>
+        <v>2.656859976468695e-08</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001444778521545231</v>
+        <v>2.275742758683919e-07</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0003428428899496794</v>
+        <v>3.108027044618211e-07</v>
       </c>
       <c r="S10" t="n">
-        <v>5.570260691456497e-05</v>
+        <v>4.316171597906759e-08</v>
       </c>
       <c r="T10" t="n">
-        <v>0.001005993923172355</v>
+        <v>1.438480978777079e-07</v>
       </c>
       <c r="U10" t="n">
-        <v>0.000447640719357878</v>
+        <v>1.202547821321787e-07</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0007754446705803275</v>
+        <v>1.479857587582956e-07</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0005758143379352987</v>
+        <v>9.014591739742173e-08</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0005651932442560792</v>
+        <v>7.255543010842302e-08</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.001364181167446077</v>
+        <v>1.55414355162975e-07</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0001954288309207186</v>
+        <v>4.705090717038729e-08</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0008941266569308937</v>
+        <v>1.754874432435827e-07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0001768557704053819</v>
+        <v>3.494586309216174e-08</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.000561334250960499</v>
+        <v>1.432717340321688e-07</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0001012962529785</v>
+        <v>1.271589269435935e-07</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.163837754982524e-05</v>
+        <v>1.854331230788375e-07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0001373793202219531</v>
+        <v>3.302708364572027e-07</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0002657523436937481</v>
+        <v>1.838222374317411e-07</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0007702623261138797</v>
+        <v>3.956733252152844e-08</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.000492806255351752</v>
+        <v>4.070374757247919e-07</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0003336209338158369</v>
+        <v>1.534614000320289e-07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0007963640964590013</v>
+        <v>8.385301697444447e-08</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.00109203509055078</v>
+        <v>2.427711365271534e-07</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0002913255011662841</v>
+        <v>3.125067848941399e-08</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.0002233302220702171</v>
+        <v>6.351896786327416e-09</v>
       </c>
       <c r="AO10" t="n">
-        <v>6.921886961208656e-05</v>
+        <v>3.376803192622901e-08</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0003653253661468625</v>
+        <v>6.631529458900332e-08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0005964116426184773</v>
+        <v>1.684917663169472e-07</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.2416817197809e-05</v>
+        <v>1.3513106011942e-07</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0006836354732513428</v>
+        <v>6.760897264257437e-08</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.000129377847770229</v>
+        <v>1.371990663301403e-07</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.004630114883184433</v>
+        <v>1.219154455611715e-06</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.642401033081114e-05</v>
+        <v>8.777709581408999e-08</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.001100725727155805</v>
+        <v>1.577759007886925e-07</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0004161261895205826</v>
+        <v>3.121464828836906e-07</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.0002403093822067603</v>
+        <v>6.521696604977478e-08</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0001780807651812211</v>
+        <v>2.493919382118293e-08</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0006812413921579719</v>
+        <v>9.710373660709593e-08</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.001045558252371848</v>
+        <v>1.400731264311617e-07</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0009402488358318806</v>
+        <v>1.212195286370843e-07</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.001236802549101412</v>
+        <v>1.762310546382651e-07</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.001264640013687313</v>
+        <v>2.287053462168842e-07</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0009692235616967082</v>
+        <v>1.889155072376525e-07</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.001684342161752284</v>
+        <v>2.859938206256629e-07</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.000469524587970227</v>
+        <v>1.220139580482282e-07</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0004358409787528217</v>
+        <v>5.619238407916782e-08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.001703759655356407</v>
+        <v>1.57579279402853e-07</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0002079898258671165</v>
+        <v>1.308872299432551e-07</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.001063572941347957</v>
+        <v>1.942928129494703e-08</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0005129054770804942</v>
+        <v>1.338093511549232e-07</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0003241001686546952</v>
+        <v>9.335516892861051e-08</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0004137679643463343</v>
+        <v>3.321543040613051e-09</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0006422497099265456</v>
+        <v>2.965379621855391e-07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0001053761079674587</v>
+        <v>3.937634929229716e-08</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0004663115541916341</v>
+        <v>2.865772330551408e-07</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0007481380016542971</v>
+        <v>6.026910170930933e-08</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0001500171929365024</v>
+        <v>1.439307624195862e-07</v>
       </c>
       <c r="BU10" t="n">
-        <v>6.63083337713033e-05</v>
+        <v>3.00753200122017e-08</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.00247100368142128</v>
+        <v>7.626896376677905e-07</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.000850339129101485</v>
+        <v>2.753720806936144e-08</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0006594430888071656</v>
+        <v>6.567121602074621e-08</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.521972394082695e-05</v>
+        <v>1.301432206446407e-07</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0004066096153110266</v>
+        <v>2.890805461674972e-08</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.001024773344397545</v>
+        <v>2.276551782642855e-07</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0001875452871900052</v>
+        <v>1.249361787358794e-07</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0007389654056169093</v>
+        <v>1.306236185882881e-07</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.0003753561759367585</v>
+        <v>1.534141347292461e-08</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.001164154149591923</v>
+        <v>4.050363031637971e-07</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0005415990017354488</v>
+        <v>1.031222183200953e-07</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0003088768280576915</v>
+        <v>2.506147822600724e-08</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0004120948433410376</v>
+        <v>1.408926237900232e-07</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0004471933643799275</v>
+        <v>8.028038678276062e-08</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0003515655407682061</v>
+        <v>7.794515255454826e-09</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.0001464069209760055</v>
+        <v>3.500698042557815e-08</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0004931184812448919</v>
+        <v>4.829938404782297e-08</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.0005613274406641722</v>
+        <v>3.010062243902212e-07</v>
       </c>
       <c r="CN10" t="n">
-        <v>9.164142102235928e-05</v>
+        <v>7.049465011732536e-07</v>
       </c>
       <c r="CO10" t="n">
-        <v>2.063682040898129e-05</v>
+        <v>1.324098661825701e-07</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.001588735962286592</v>
+        <v>9.853286542238493e-08</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.001300463220104575</v>
+        <v>1.512120491042879e-07</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0002103596634697169</v>
+        <v>2.688755671442777e-07</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0009095710702240467</v>
+        <v>9.426639024923134e-08</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.0009495150879956782</v>
+        <v>1.394697051182447e-07</v>
       </c>
       <c r="CU10" t="n">
-        <v>8.703242929186672e-05</v>
+        <v>6.707151101181807e-08</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.0002982495934702456</v>
+        <v>7.205866836557107e-08</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.001033029984682798</v>
+        <v>4.022683128823701e-07</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0004297961131669581</v>
+        <v>1.001803724420824e-07</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0007221322739496827</v>
+        <v>2.507884389046922e-08</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0004904166562482715</v>
+        <v>1.137572240850204e-07</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0005453460034914315</v>
+        <v>7.901908105623079e-08</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0003920095041394234</v>
+        <v>5.358229770990874e-08</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0001984678528970107</v>
+        <v>5.555520488087495e-08</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.000275643658824265</v>
+        <v>9.322953076207341e-08</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0005701272748410702</v>
+        <v>2.945858739167306e-07</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.000568169285543263</v>
+        <v>1.321744349525034e-07</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.001354641513898969</v>
+        <v>7.770577070687068e-09</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.003973149694502354</v>
+        <v>1.722540901027969e-07</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001185130327939987</v>
+        <v>1.325474840996321e-07</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0005342215299606323</v>
+        <v>5.017806188334362e-07</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0001974476763280109</v>
+        <v>5.298745975323982e-08</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001155172591097653</v>
+        <v>6.169724287019562e-08</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0002480569528415799</v>
+        <v>1.608982387324431e-07</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0005354080349206924</v>
+        <v>1.184433244816319e-07</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0005604323814623058</v>
+        <v>1.810349203879014e-07</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0005797920748591423</v>
+        <v>1.259954416354958e-07</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0002752716827671975</v>
+        <v>1.367908595284462e-07</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.00114341510925442</v>
+        <v>3.737978104823014e-08</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.0007443670183420181</v>
+        <v>4.667064956720424e-08</v>
       </c>
       <c r="DT10" t="n">
-        <v>2.736445094342344e-05</v>
+        <v>7.681357772071351e-08</v>
       </c>
       <c r="DU10" t="n">
-        <v>5.003851401852444e-05</v>
+        <v>5.186481644159358e-08</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0009973444975912571</v>
+        <v>7.894115583439998e-08</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.000423446879722178</v>
+        <v>9.210028650841195e-08</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.0001999051310122013</v>
+        <v>3.112138244887319e-07</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.001180252525955439</v>
+        <v>1.108675995453723e-08</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0001205312146339566</v>
+        <v>4.380144957849552e-08</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.001105901319533587</v>
+        <v>2.915403740644251e-07</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0009096215944737196</v>
+        <v>1.325099958648934e-07</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.000382631435059011</v>
+        <v>1.710914787622642e-08</v>
       </c>
       <c r="ED10" t="n">
-        <v>9.962783224182203e-06</v>
+        <v>1.80362064838846e-07</v>
       </c>
       <c r="EE10" t="n">
-        <v>5.022444020141847e-05</v>
+        <v>2.03404169951682e-07</v>
       </c>
       <c r="EF10" t="n">
-        <v>4.658976104110479e-05</v>
+        <v>2.261637455092114e-08</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0006991950795054436</v>
+        <v>1.9780146942594e-07</v>
       </c>
       <c r="EH10" t="n">
-        <v>7.250704220496118e-05</v>
+        <v>2.666545384499841e-08</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0002447145816404372</v>
+        <v>1.620423084602862e-08</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0005750072887167335</v>
+        <v>1.248258474362274e-08</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0003820627753157169</v>
+        <v>5.744120556983034e-08</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0007489550043828785</v>
+        <v>7.096092247138586e-08</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.00024174724239856</v>
+        <v>6.190107626480312e-08</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0001540845551062375</v>
+        <v>1.4322252184229e-07</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0002172692766180262</v>
+        <v>8.321669042743451e-08</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0003401201975066215</v>
+        <v>1.491068388759231e-07</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0005661945324391127</v>
+        <v>5.820004389534006e-08</v>
       </c>
       <c r="ER10" t="n">
-        <v>2.227304685220588e-05</v>
+        <v>6.342642677736876e-08</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0007791409734636545</v>
+        <v>1.21183518331236e-07</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001010216656140983</v>
+        <v>2.117658937095257e-07</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0004062783264089376</v>
+        <v>4.685839627427413e-08</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.00138921570032835</v>
+        <v>3.873434906154216e-08</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.000532028148882091</v>
+        <v>5.495767751995118e-08</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0002493600186426193</v>
+        <v>4.421685417810295e-08</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.00100607774220407</v>
+        <v>4.637189761069749e-07</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0003013047389686108</v>
+        <v>8.574275511818996e-08</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0004908886621706188</v>
+        <v>9.981491189137159e-09</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0002607955248095095</v>
+        <v>8.490131619964814e-08</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.000501469592563808</v>
+        <v>8.207769752743843e-08</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0004777185968123376</v>
+        <v>1.015557060668471e-08</v>
       </c>
       <c r="FE10" t="n">
-        <v>8.900728425942361e-05</v>
+        <v>6.488500048362766e-08</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0004958634963259101</v>
+        <v>1.030446270533503e-07</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0003260133089497685</v>
+        <v>3.002075743552268e-08</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0007109816069714725</v>
+        <v>1.67948186913236e-07</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0008781743235886097</v>
+        <v>1.025399569698493e-07</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.001281318836845458</v>
+        <v>2.280086874861809e-07</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0001585353311384097</v>
+        <v>1.057376977087188e-07</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0001256520044989884</v>
+        <v>1.640837297145481e-07</v>
       </c>
       <c r="FM10" t="n">
-        <v>6.432950613088906e-06</v>
+        <v>1.294598632739508e-07</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0007129862788133323</v>
+        <v>6.143884689890911e-08</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0006515850545838475</v>
+        <v>1.452012128311253e-07</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0001435428857803345</v>
+        <v>2.011265394230577e-07</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.000205484961043112</v>
+        <v>2.613369076698291e-07</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.0001237436954397708</v>
+        <v>1.226820756095037e-09</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0002694764989428222</v>
+        <v>1.496736246053842e-08</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.002049244940280914</v>
+        <v>3.632274001574842e-07</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0004353058466222137</v>
+        <v>5.769818045564534e-08</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0008302860078401864</v>
+        <v>7.620187147949764e-08</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.000596419966313988</v>
+        <v>6.882603997837577e-08</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0005138097330927849</v>
+        <v>1.860108795881388e-07</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.001152518205344677</v>
+        <v>1.069966160116564e-08</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0001592826301930472</v>
+        <v>1.817350039345911e-07</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0001033569715218619</v>
+        <v>2.719521319249907e-08</v>
       </c>
       <c r="GB10" t="n">
-        <v>7.847587403375655e-05</v>
+        <v>8.550945551633049e-08</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.000501305446960032</v>
+        <v>9.351732899176568e-08</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0008530803606845438</v>
+        <v>7.322140760379625e-08</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.002237117383629084</v>
+        <v>5.513712153515371e-08</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0005435729399323463</v>
+        <v>1.710874641958071e-07</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0007375301793217659</v>
+        <v>1.772663154042675e-07</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.03503759205341339</v>
+        <v>0.1725192815065384</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2878698110580444</v>
+        <v>0.5737245082855225</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02841063402593136</v>
+        <v>0.07690402120351791</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2110468745231628</v>
+        <v>0.2240252494812012</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01583291217684746</v>
+        <v>0.1640184670686722</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2242178618907928</v>
+        <v>0.1112790703773499</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005934014916419983</v>
+        <v>0.1338193565607071</v>
       </c>
       <c r="H11" t="n">
-        <v>0.09306369721889496</v>
+        <v>0.1239298135042191</v>
       </c>
       <c r="I11" t="n">
-        <v>0.06313537061214447</v>
+        <v>0.1997434347867966</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07852204144001007</v>
+        <v>0.08189269155263901</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2441282868385315</v>
+        <v>0.7123867869377136</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01973582990467548</v>
+        <v>0.08687186241149902</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1922814548015594</v>
+        <v>0.2719367444515228</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02655866369605064</v>
+        <v>0.2076183408498764</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2247574478387833</v>
+        <v>0.03889255970716476</v>
       </c>
       <c r="P11" t="n">
-        <v>0.01990429498255253</v>
+        <v>0.08903861790895462</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.002662081271409988</v>
+        <v>0.08485545217990875</v>
       </c>
       <c r="R11" t="n">
-        <v>0.04143825173377991</v>
+        <v>0.3581820130348206</v>
       </c>
       <c r="S11" t="n">
-        <v>0.007010072935372591</v>
+        <v>0.0521867424249649</v>
       </c>
       <c r="T11" t="n">
-        <v>0.01135395094752312</v>
+        <v>0.05654764547944069</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03831081837415695</v>
+        <v>0.01381384953856468</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0455259308218956</v>
+        <v>0.1058779805898666</v>
       </c>
       <c r="W11" t="n">
-        <v>0.05688735097646713</v>
+        <v>0.08000370860099792</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01494495943188667</v>
+        <v>0.0109065305441618</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0293260533362627</v>
+        <v>0.02526266686618328</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.04839498177170753</v>
+        <v>0.08462584763765335</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.04103862121701241</v>
+        <v>0.04404294863343239</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01816538162529469</v>
+        <v>0.03115104138851166</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.006204428151249886</v>
+        <v>0.04849774017930031</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.02975779585540295</v>
+        <v>0.07670779526233673</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.003202226012945175</v>
+        <v>0.02066803351044655</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0213671587407589</v>
+        <v>0.3190891146659851</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0229056216776371</v>
+        <v>0.1671344488859177</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.005995112471282482</v>
+        <v>0.06080615893006325</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.008548992685973644</v>
+        <v>0.1233745664358139</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01849328726530075</v>
+        <v>0.0006242187228053808</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.04450447484850883</v>
+        <v>0.1037899330258369</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.0307004526257515</v>
+        <v>0.0009360285475850105</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.01755374856293201</v>
+        <v>0.007374782115221024</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.02719581127166748</v>
+        <v>0.08726456761360168</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0140587342903018</v>
+        <v>0.01813731156289577</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.035027876496315</v>
+        <v>0.1275691092014313</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.01297847647219896</v>
+        <v>0.09188240021467209</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.03613563627004623</v>
+        <v>0.239486426115036</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.03679558634757996</v>
+        <v>0.01741377077996731</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.004686977714300156</v>
+        <v>0.1927603185176849</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1734753102064133</v>
+        <v>0.4816015362739563</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.02050043642520905</v>
+        <v>0.004313571378588676</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.06507453322410583</v>
+        <v>0.01065013650804758</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.03580624610185623</v>
+        <v>0.04048298671841621</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.1182695925235748</v>
+        <v>0.09376457333564758</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.04429260268807411</v>
+        <v>0.04547049105167389</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.006900141015648842</v>
+        <v>0.007425129413604736</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.07166409492492676</v>
+        <v>0.01555003970861435</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.02837608009576797</v>
+        <v>0.05283792316913605</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.07495740056037903</v>
+        <v>0.1382533013820648</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.07766970247030258</v>
+        <v>0.0388638861477375</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.03124995157122612</v>
+        <v>0.2483037561178207</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.02555378340184689</v>
+        <v>0.01913802698254585</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.01967067271471024</v>
+        <v>0.1852555274963379</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.04139333218336105</v>
+        <v>0.1267004460096359</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.03475144505500793</v>
+        <v>0.02663577720522881</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.03822604939341545</v>
+        <v>0.08154866099357605</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.01680020429193974</v>
+        <v>0.02235094271600246</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.05074473097920418</v>
+        <v>0.03513934463262558</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.03919071704149246</v>
+        <v>0.01392468903213739</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.02198103815317154</v>
+        <v>0.03847517073154449</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0007110866717994213</v>
+        <v>0.1335021555423737</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.00625367509201169</v>
+        <v>0.09544049948453903</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01236157771199942</v>
+        <v>0.2020025700330734</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.02505356632173061</v>
+        <v>0.01406359858810902</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.008945063687860966</v>
+        <v>0.03192658722400665</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.01128403097391129</v>
+        <v>0.1003482714295387</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.0991031751036644</v>
+        <v>0.2998394072055817</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.04743406921625137</v>
+        <v>0.01416956447064877</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.06150784716010094</v>
+        <v>0.0709746927022934</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.01870997436344624</v>
+        <v>0.06528225541114807</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.07699904590845108</v>
+        <v>0.05993187054991722</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.002669619396328926</v>
+        <v>0.03286494687199593</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.01437217183411121</v>
+        <v>0.02029947564005852</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.04909648001194</v>
+        <v>0.0578935332596302</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.007729707285761833</v>
+        <v>0.004530958831310272</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.03973939269781113</v>
+        <v>0.1313378363847733</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.04272890836000443</v>
+        <v>0.001748774200677872</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.02597853541374207</v>
+        <v>0.07195357233285904</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0151032991707325</v>
+        <v>0.03781434893608093</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.03498231619596481</v>
+        <v>0.01216511242091656</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.01581355184316635</v>
+        <v>0.06143211200833321</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.02216873876750469</v>
+        <v>0.01060362253338099</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.02928592078387737</v>
+        <v>0.0381987988948822</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.04853870719671249</v>
+        <v>0.1219176650047302</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.01189352199435234</v>
+        <v>0.2711324095726013</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.008570659905672073</v>
+        <v>0.01225089468061924</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.04726212099194527</v>
+        <v>0.1547521650791168</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.005407275632023811</v>
+        <v>0.02103456109762192</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.02515658736228943</v>
+        <v>0.1882622838020325</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.0575990341603756</v>
+        <v>0.08325424790382385</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.04139137640595436</v>
+        <v>0.07767118513584137</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.001340856542810798</v>
+        <v>0.02607616782188416</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.002387698739767075</v>
+        <v>0.03354061022400856</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.03787553682923317</v>
+        <v>0.1401240825653076</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.04268170893192291</v>
+        <v>0.01396181806921959</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.03924132883548737</v>
+        <v>0.06160934641957283</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01325806695967913</v>
+        <v>0.05843520164489746</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.03799805045127869</v>
+        <v>0.0004908870905637741</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.01461446564644575</v>
+        <v>0.006199173629283905</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.03841298073530197</v>
+        <v>0.02180050313472748</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01762210577726364</v>
+        <v>0.02876162715256214</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.01222854200750589</v>
+        <v>0.08869007229804993</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.002635680604726076</v>
+        <v>0.2329486608505249</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.01392016932368279</v>
+        <v>0.07196254283189774</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.1114445254206657</v>
+        <v>0.08695490658283234</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.04123392701148987</v>
+        <v>0.2107227742671967</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.00722238514572382</v>
+        <v>0.2915050685405731</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.03365952149033546</v>
+        <v>0.02778004482388496</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.04184626042842865</v>
+        <v>0.02213600650429726</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.03844232112169266</v>
+        <v>0.2225495427846909</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.002584485337138176</v>
+        <v>0.1508281081914902</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.01379777863621712</v>
+        <v>0.04764828830957413</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.025925412774086</v>
+        <v>0.03778093680739403</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.008744482882320881</v>
+        <v>0.09659135341644287</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.009078232571482658</v>
+        <v>0.02349866181612015</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.002909091301262379</v>
+        <v>0.09726140648126602</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.008404587395489216</v>
+        <v>0.03621722385287285</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.006449188571423292</v>
+        <v>0.07519112527370453</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.03863100335001945</v>
+        <v>0.01990576833486557</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.005588932894170284</v>
+        <v>0.1354794204235077</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.01492229104042053</v>
+        <v>0.009682786650955677</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.05117551237344742</v>
+        <v>0.02249638363718987</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.01070114597678185</v>
+        <v>0.1708209812641144</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01890799030661583</v>
+        <v>0.03978753462433815</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.04165671020746231</v>
+        <v>0.04016773402690887</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.01329652313143015</v>
+        <v>0.07178634405136108</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.01323417015373707</v>
+        <v>0.1326789557933807</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.001743632834404707</v>
+        <v>0.1832537353038788</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.01274652220308781</v>
+        <v>0.01368060521781445</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.03960774093866348</v>
+        <v>0.07990510761737823</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.03612529113888741</v>
+        <v>0.0107096005231142</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.007514290511608124</v>
+        <v>0.1440850794315338</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.009649543091654778</v>
+        <v>0.05913541465997696</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.0324125811457634</v>
+        <v>0.08734721690416336</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.01965301856398582</v>
+        <v>0.05430804193019867</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.01544262934476137</v>
+        <v>0.05831976607441902</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.01312988717108965</v>
+        <v>0.1069375798106194</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.003741740249097347</v>
+        <v>0.01764938235282898</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01277701836079359</v>
+        <v>0.03840098157525063</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.03853922337293625</v>
+        <v>0.02221672609448433</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0421837717294693</v>
+        <v>0.01239116489887238</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.006993392016738653</v>
+        <v>0.1734470427036285</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.04671475663781166</v>
+        <v>0.2371252775192261</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.05037492886185646</v>
+        <v>0.07158477604389191</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.08753878623247147</v>
+        <v>0.0471586100757122</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.008368594571948051</v>
+        <v>0.01893890462815762</v>
       </c>
       <c r="EX11" t="n">
-        <v>7.642759010195732e-05</v>
+        <v>0.02370165660977364</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.02819553390145302</v>
+        <v>0.1884703636169434</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.03561339154839516</v>
+        <v>0.01784994080662727</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.03800194337964058</v>
+        <v>0.09019127488136292</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01733937487006187</v>
+        <v>0.07134514302015305</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02774890325963497</v>
+        <v>0.01984378881752491</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.03225032240152359</v>
+        <v>0.06512454152107239</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.02681883797049522</v>
+        <v>0.004572325386106968</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.02886839956045151</v>
+        <v>0.02584903128445148</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.01664330624043941</v>
+        <v>0.0168067179620266</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.03676785156130791</v>
+        <v>0.2256228029727936</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.03950158506631851</v>
+        <v>0.08599020540714264</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.04897402971982956</v>
+        <v>0.06890598684549332</v>
       </c>
       <c r="FK11" t="n">
-        <v>6.66789710521698e-05</v>
+        <v>0.06948647648096085</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0106075732037425</v>
+        <v>0.0459054633975029</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.003275764174759388</v>
+        <v>0.01568479649722576</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.02122646197676659</v>
+        <v>0.07004447281360626</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.01482049748301506</v>
+        <v>0.2000942826271057</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.01649363711476326</v>
+        <v>0.04824965074658394</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.04469237104058266</v>
+        <v>0.005555309355258942</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.05493085831403732</v>
+        <v>0.2045428305864334</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.07065808027982712</v>
+        <v>0.3986682593822479</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.04558566957712173</v>
+        <v>0.07596103847026825</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.04586994647979736</v>
+        <v>0.09427955746650696</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.06742624938488007</v>
+        <v>0.2092233598232269</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.02473198063671589</v>
+        <v>0.1025669947266579</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.0005829652072861791</v>
+        <v>0.04244515672326088</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.0532233752310276</v>
+        <v>0.08428576588630676</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.02596116811037064</v>
+        <v>0.004904769826680422</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.02092098072171211</v>
+        <v>0.03672118112444878</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0302403811365366</v>
+        <v>0.006879311054944992</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.009237904101610184</v>
+        <v>0.03043351136147976</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.002320791594684124</v>
+        <v>0.0460609532892704</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1463215798139572</v>
+        <v>0.0495578721165657</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.01123653631657362</v>
+        <v>0.1563807129859924</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0009648737031966448</v>
+        <v>0.1012813001871109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.1701481640338898</v>
+        <v>0.4638580679893494</v>
       </c>
       <c r="B12" t="n">
-        <v>0.7443641424179077</v>
+        <v>0.4882342517375946</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07091319561004639</v>
+        <v>0.2457621991634369</v>
       </c>
       <c r="D12" t="n">
-        <v>0.14692422747612</v>
+        <v>0.01003257185220718</v>
       </c>
       <c r="E12" t="n">
-        <v>0.160122349858284</v>
+        <v>0.0401051789522171</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02182192169129848</v>
+        <v>0.2076114565134048</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07436197996139526</v>
+        <v>0.1812873780727386</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02781800553202629</v>
+        <v>0.10942742228508</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0145849920809269</v>
+        <v>0.262098640203476</v>
       </c>
       <c r="J12" t="n">
-        <v>0.004579052329063416</v>
+        <v>0.4821972250938416</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6745132207870483</v>
+        <v>0.6803866624832153</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05325387790799141</v>
+        <v>0.3349361419677734</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1046551689505577</v>
+        <v>0.05552466958761215</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1037727147340775</v>
+        <v>0.07469438016414642</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05956656858325005</v>
+        <v>0.2575980126857758</v>
       </c>
       <c r="P12" t="n">
-        <v>0.04511134326457977</v>
+        <v>0.1005929112434387</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1079429239034653</v>
+        <v>0.1670739650726318</v>
       </c>
       <c r="R12" t="n">
-        <v>0.07392238825559616</v>
+        <v>0.6241288781166077</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09311242401599884</v>
+        <v>0.0006261270027607679</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2432929277420044</v>
+        <v>0.08192189782857895</v>
       </c>
       <c r="U12" t="n">
-        <v>0.02118471078574657</v>
+        <v>0.05743896216154099</v>
       </c>
       <c r="V12" t="n">
-        <v>0.03633318096399307</v>
+        <v>0.0782349556684494</v>
       </c>
       <c r="W12" t="n">
-        <v>0.06524045765399933</v>
+        <v>0.3903815150260925</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1029199659824371</v>
+        <v>0.0917992889881134</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.04317113757133484</v>
+        <v>0.06472484767436981</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.1108617261052132</v>
+        <v>0.009333565831184387</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0245968047529459</v>
+        <v>0.001085016876459122</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.06672237813472748</v>
+        <v>0.08007080852985382</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.04490257054567337</v>
+        <v>0.03493617475032806</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1141675040125847</v>
+        <v>0.1487269401550293</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.065437912940979</v>
+        <v>0.1241389214992523</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09370837360620499</v>
+        <v>0.3735426068305969</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.03219236433506012</v>
+        <v>0.08374015241861343</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.06649072468280792</v>
+        <v>0.04086767137050629</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.001627136021852493</v>
+        <v>0.118071161210537</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.009637138806283474</v>
+        <v>0.03635738417506218</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.2048728913068771</v>
+        <v>0.0811871737241745</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.112565889954567</v>
+        <v>0.01687170937657356</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.001110218465328217</v>
+        <v>0.1575438380241394</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.05099233239889145</v>
+        <v>0.1764155626296997</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.071876160800457</v>
+        <v>0.5470327734947205</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.04521457850933075</v>
+        <v>0.1624608039855957</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.03042392618954182</v>
+        <v>0.02039995416998863</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.1014833822846413</v>
+        <v>0.2371404469013214</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.04553401097655296</v>
+        <v>0.02381381392478943</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.1170061230659485</v>
+        <v>0.2102051079273224</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5201943516731262</v>
+        <v>0.1211862340569496</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.09104088693857193</v>
+        <v>0.0996265783905983</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.06486454606056213</v>
+        <v>0.01633355766534805</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.0231121089309454</v>
+        <v>0.3527912497520447</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.09407819807529449</v>
+        <v>0.07068098336458206</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1018370687961578</v>
+        <v>0.04016145318746567</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.02615071460604668</v>
+        <v>0.1243896335363388</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.01308490615338087</v>
+        <v>0.1312309354543686</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.1306819319725037</v>
+        <v>0.1002188697457314</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1011606454849243</v>
+        <v>0.3961840569972992</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.1108641549944878</v>
+        <v>0.1420604884624481</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.01189397275447845</v>
+        <v>0.1092190742492676</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.008171983994543552</v>
+        <v>0.6623508930206299</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.0367860421538353</v>
+        <v>0.2506203651428223</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.07733365148305893</v>
+        <v>0.1502206027507782</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.1022975370287895</v>
+        <v>0.111026406288147</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.04215554520487785</v>
+        <v>0.06468206644058228</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.08962105214595795</v>
+        <v>0.009412080049514771</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.08416619896888733</v>
+        <v>0.2259615212678909</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.006427225191146135</v>
+        <v>0.01367140002548695</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.009284555912017822</v>
+        <v>0.002968519926071167</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1031181216239929</v>
+        <v>0.524710476398468</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.1332611888647079</v>
+        <v>0.004194857552647591</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.06820253282785416</v>
+        <v>0.00962904654443264</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.07515139877796173</v>
+        <v>0.1850658059120178</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.03686202317476273</v>
+        <v>0.009332656860351562</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.08919810503721237</v>
+        <v>0.171202763915062</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.3787499964237213</v>
+        <v>0.0828481987118721</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.05707784742116928</v>
+        <v>0.03862439095973969</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.07739073038101196</v>
+        <v>0.00974784791469574</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07231204211711884</v>
+        <v>0.2199525088071823</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.01484955847263336</v>
+        <v>0.1645375043153763</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.05980560928583145</v>
+        <v>0.1508684754371643</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.02757227048277855</v>
+        <v>0.1136698126792908</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.004259291104972363</v>
+        <v>0.1702145785093307</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.03599910065531731</v>
+        <v>0.1708856672048569</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.1345174908638</v>
+        <v>0.07303041219711304</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.05055647343397141</v>
+        <v>0.007690055761486292</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.03118791431188583</v>
+        <v>0.00825018435716629</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.01461312081664801</v>
+        <v>0.0007375478744506836</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.005922618787735701</v>
+        <v>0.02010903880000114</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.05592863261699677</v>
+        <v>0.0128632690757513</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.00278804381377995</v>
+        <v>0.08697032183408737</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.02757170796394348</v>
+        <v>0.1152860671281815</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.2104114890098572</v>
+        <v>0.06427465379238129</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.1059675887227058</v>
+        <v>0.2211895287036896</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.001121246255934238</v>
+        <v>0.06107258796691895</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.1142900288105011</v>
+        <v>0.08122109621763229</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.4709072113037109</v>
+        <v>0.5851064920425415</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.01527493447065353</v>
+        <v>0.461447149515152</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.06290653347969055</v>
+        <v>0.07227516174316406</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.1176205724477768</v>
+        <v>0.04369358345866203</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.1169029176235199</v>
+        <v>0.1372368037700653</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.04565495997667313</v>
+        <v>0.1580699384212494</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.1289989054203033</v>
+        <v>0.08116549998521805</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.0798490047454834</v>
+        <v>0.03080108948051929</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.04176175221800804</v>
+        <v>0.01448988541960716</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.05418399721384048</v>
+        <v>0.002596203237771988</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.01149894203990698</v>
+        <v>0.007127474993467331</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.04003128781914711</v>
+        <v>0.0156757514923811</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.02458670921623707</v>
+        <v>0.01411618664860725</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.02123186551034451</v>
+        <v>0.08149039745330811</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1192423850297928</v>
+        <v>0.09360896795988083</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.2559556365013123</v>
+        <v>0.05401791632175446</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.00377549254335463</v>
+        <v>0.1178552061319351</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.2432723641395569</v>
+        <v>0.1175446510314941</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1477059423923492</v>
+        <v>0.05394443869590759</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.07203700393438339</v>
+        <v>0.3353282809257507</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.06565473228693008</v>
+        <v>0.1039498597383499</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.06457794457674026</v>
+        <v>0.1271385550498962</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.04136913269758224</v>
+        <v>0.4390549063682556</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.04339036718010902</v>
+        <v>0.07045602053403854</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.03488440066576004</v>
+        <v>0.1996560990810394</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.09171772748231888</v>
+        <v>0.1038633584976196</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01153643988072872</v>
+        <v>0.01998946070671082</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.1191478073596954</v>
+        <v>0.0402342900633812</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.0130185354501009</v>
+        <v>0.1677978336811066</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.09945487976074219</v>
+        <v>0.07258002460002899</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.09548002481460571</v>
+        <v>0.1088836118578911</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.01710281148552895</v>
+        <v>0.1715890318155289</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0112232007086277</v>
+        <v>0.05692889541387558</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.2547401487827301</v>
+        <v>0.1633146852254868</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.06292518973350525</v>
+        <v>0.02147571556270123</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0717327743768692</v>
+        <v>0.1426299512386322</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.107110969722271</v>
+        <v>0.08664123713970184</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.03934914991259575</v>
+        <v>0.2521233856678009</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.03829977661371231</v>
+        <v>0.09845302999019623</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.03579921275377274</v>
+        <v>0.353397011756897</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.01703845150768757</v>
+        <v>0.158166766166687</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.1049929037690163</v>
+        <v>0.1563267856836319</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.05550472438335419</v>
+        <v>0.07435063272714615</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.0007705320604145527</v>
+        <v>0.06006716936826706</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.01171920448541641</v>
+        <v>0.04652080312371254</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01225073449313641</v>
+        <v>0.05972511321306229</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.04279712587594986</v>
+        <v>0.02416281215846539</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.03810983896255493</v>
+        <v>0.0147858178243041</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.004697788506746292</v>
+        <v>0.06513366103172302</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.01152573153376579</v>
+        <v>0.2489715665578842</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.005923934280872345</v>
+        <v>0.1513993442058563</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.02229899913072586</v>
+        <v>0.0251303669065237</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.1533242762088776</v>
+        <v>0.198125347495079</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02242030948400497</v>
+        <v>0.1640340983867645</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.08215361833572388</v>
+        <v>0.121810145676136</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.03552158176898956</v>
+        <v>0.363975465297699</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.1050203666090965</v>
+        <v>0.1002455577254295</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.1072037816047668</v>
+        <v>0.1548811942338943</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.00504562072455883</v>
+        <v>0.06953300535678864</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.04473860934376717</v>
+        <v>0.1764372140169144</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.1298893094062805</v>
+        <v>0.1167783588171005</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.06304652243852615</v>
+        <v>0.01635205000638962</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.01475325413048267</v>
+        <v>0.01317083835601807</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.05881163477897644</v>
+        <v>0.06569138914346695</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.002354762284085155</v>
+        <v>0.007567442953586578</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.05739389359951019</v>
+        <v>0.001639766967855394</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.007593855261802673</v>
+        <v>0.05684445053339005</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.02685671858489513</v>
+        <v>0.1418796330690384</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.005926419515162706</v>
+        <v>0.01477750577032566</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.009088188409805298</v>
+        <v>0.05792176723480225</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.1061133146286011</v>
+        <v>0.007833548821508884</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.001894999295473099</v>
+        <v>0.03468269109725952</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.01926117576658726</v>
+        <v>0.04512200504541397</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.06012894958257675</v>
+        <v>0.1291337609291077</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.1219180524349213</v>
+        <v>0.09223675727844238</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.01878061704337597</v>
+        <v>0.09957899153232574</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.03327404335141182</v>
+        <v>0.2219298034906387</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.04673397913575172</v>
+        <v>0.1566881537437439</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.1179535314440727</v>
+        <v>0.2132770717144012</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.08729781210422516</v>
+        <v>0.104757696390152</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.0553717166185379</v>
+        <v>0.4380554556846619</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.1067073121666908</v>
+        <v>0.3287974298000336</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0173888336867094</v>
+        <v>0.08916239440441132</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.04362359642982483</v>
+        <v>0.001683257520198822</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.06302358955144882</v>
+        <v>0.0007219910621643066</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.05025319755077362</v>
+        <v>0.06755032390356064</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.1209505349397659</v>
+        <v>0.05957534164190292</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.008004054427146912</v>
+        <v>0.05281525105237961</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.06481336057186127</v>
+        <v>0.124573603272438</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.09525424987077713</v>
+        <v>0.1285316795110703</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.1863314807415009</v>
+        <v>0.2068851888179779</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.1032042056322098</v>
+        <v>0.1967923045158386</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.1663946807384491</v>
+        <v>0.0803506001830101</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.001742620021104813</v>
+        <v>0.09772306680679321</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0005391351878643036</v>
+        <v>0.2966118454933167</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0002660990285221487</v>
+        <v>0.002069412497803569</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00288097676821053</v>
+        <v>0.05893747135996819</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0002451620239298791</v>
+        <v>0.02698648162186146</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001000021584331989</v>
+        <v>0.01533268578350544</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0008338357438333333</v>
+        <v>0.007256211712956429</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001308020437136292</v>
+        <v>0.049027219414711</v>
       </c>
       <c r="G13" t="n">
-        <v>7.024716614978388e-05</v>
+        <v>0.01405114494264126</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0007643532007932663</v>
+        <v>0.01298917923122644</v>
       </c>
       <c r="I13" t="n">
-        <v>3.279427255620249e-05</v>
+        <v>0.02599898353219032</v>
       </c>
       <c r="J13" t="n">
-        <v>0.000489418744109571</v>
+        <v>0.008203084580600262</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002702260389924049</v>
+        <v>0.05343114212155342</v>
       </c>
       <c r="L13" t="n">
-        <v>3.691460733534768e-05</v>
+        <v>0.03637871146202087</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0006240148213692009</v>
+        <v>0.04202636331319809</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0002090773195959628</v>
+        <v>0.01105285622179508</v>
       </c>
       <c r="O13" t="n">
-        <v>0.001403950620442629</v>
+        <v>0.0577915832400322</v>
       </c>
       <c r="P13" t="n">
-        <v>5.908752063987777e-05</v>
+        <v>0.01510570384562016</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0001877195609267801</v>
+        <v>0.0004188958555459976</v>
       </c>
       <c r="R13" t="n">
-        <v>5.570884241024032e-05</v>
+        <v>0.03207089379429817</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001122639805544168</v>
+        <v>0.009371273219585419</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0002630292146932334</v>
+        <v>0.01315608434379101</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0001246163592441007</v>
+        <v>0.002793795429170132</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0003608406404964626</v>
+        <v>0.004390249960124493</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0001631926133995876</v>
+        <v>0.006261127069592476</v>
       </c>
       <c r="X13" t="n">
-        <v>1.551336026750505e-05</v>
+        <v>0.002854146063327789</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.686484554549679e-05</v>
+        <v>0.01216620393097401</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.000279078318271786</v>
+        <v>0.003056851681321859</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0001489651040174067</v>
+        <v>0.007551738061010838</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.577522536739707e-05</v>
+        <v>0.006531764753162861</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.700368274119683e-05</v>
+        <v>0.002744207624346018</v>
       </c>
       <c r="AD13" t="n">
-        <v>7.860566256567836e-05</v>
+        <v>0.01606844738125801</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.0002366640255786479</v>
+        <v>0.01825009658932686</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0001851058041211218</v>
+        <v>0.01691746897995472</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.308559876633808e-05</v>
+        <v>0.0246132854372263</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.277895691804588e-05</v>
+        <v>0.005141037981957197</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0001254322123713791</v>
+        <v>0.04294830560684204</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0001311070227529854</v>
+        <v>0.001324491808190942</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0005079465918242931</v>
+        <v>0.006999513134360313</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0002204241027357057</v>
+        <v>0.01168600935488939</v>
       </c>
       <c r="AM13" t="n">
-        <v>4.019813059130684e-05</v>
+        <v>0.001198268262669444</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.369960930082016e-05</v>
+        <v>0.004693579394370317</v>
       </c>
       <c r="AO13" t="n">
-        <v>2.828535798471421e-06</v>
+        <v>0.007792739197611809</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.0004068291164003313</v>
+        <v>0.006596834398806095</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.544897067011334e-05</v>
+        <v>0.001024090452119708</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.0002232803526567295</v>
+        <v>0.01303777657449245</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.0003092957485932857</v>
+        <v>0.00463771028444171</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0001002105273073539</v>
+        <v>0.007534065749496222</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.001569813583046198</v>
+        <v>0.05571311712265015</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0003588508407119662</v>
+        <v>0.01952949352562428</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.100224370835349e-05</v>
+        <v>0.0155699523165822</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0003554019785951823</v>
+        <v>0.02957079187035561</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.000680214143358171</v>
+        <v>0.04069451242685318</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0001387455267831683</v>
+        <v>0.003565492574125528</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0003398903645575047</v>
+        <v>0.01591968163847923</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0002747273247223347</v>
+        <v>0.006238684989511967</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0001025680830935016</v>
+        <v>0.01034658215939999</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0005774832679890096</v>
+        <v>0.008564489893615246</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0007325223414227366</v>
+        <v>0.01686888560652733</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0001922134542837739</v>
+        <v>0.004335670731961727</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.0003948045196011662</v>
+        <v>0.02250874787569046</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0001769762893673033</v>
+        <v>0.005433250218629837</v>
       </c>
       <c r="BI13" t="n">
-        <v>8.795865869615227e-05</v>
+        <v>0.01378400251269341</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0001708927738945931</v>
+        <v>0.002151275519281626</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.695072079310194e-05</v>
+        <v>0.01758264563977718</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0001875182933872566</v>
+        <v>0.001771974144503474</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0002692179987207055</v>
+        <v>0.01864971965551376</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0002592150995042175</v>
+        <v>0.01034458726644516</v>
       </c>
       <c r="BO13" t="n">
-        <v>9.85042643151246e-05</v>
+        <v>0.003823583712801337</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0001022936630761251</v>
+        <v>0.006869225762784481</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.635078453749884e-05</v>
+        <v>0.01150861661881208</v>
       </c>
       <c r="BR13" t="n">
-        <v>9.676323679741472e-05</v>
+        <v>0.008817260153591633</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0001474491436965764</v>
+        <v>0.002300411928445101</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.0002986180479638278</v>
+        <v>0.004822258837521076</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.898810584563762e-05</v>
+        <v>0.004018391016870737</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.0009583362261764705</v>
+        <v>0.0369972363114357</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0002965215244330466</v>
+        <v>0.004435104317963123</v>
       </c>
       <c r="BX13" t="n">
-        <v>6.792021304136142e-05</v>
+        <v>0.007955355569720268</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0001368329685647041</v>
+        <v>0.005388013087213039</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0003578126197680831</v>
+        <v>0.01690999791026115</v>
       </c>
       <c r="CA13" t="n">
-        <v>6.182469223858789e-05</v>
+        <v>0.01758292317390442</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0001446484675398096</v>
+        <v>0.000477177556604147</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0001359052839688957</v>
+        <v>0.007754215504974127</v>
       </c>
       <c r="CD13" t="n">
-        <v>7.029128028079867e-05</v>
+        <v>0.0008009641896933317</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0005389059660956264</v>
+        <v>0.01932648383080959</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0001962780515896156</v>
+        <v>0.008720237761735916</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0001226105960085988</v>
+        <v>0.004883112385869026</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0001072261147783138</v>
+        <v>0.001817913027480245</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0001057721237884834</v>
+        <v>0.009662001393735409</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0001420862972736359</v>
+        <v>8.137135591823608e-05</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0001732035016175359</v>
+        <v>0.002209902508184314</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0001397391897626221</v>
+        <v>0.003518940880894661</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0005553819937631488</v>
+        <v>0.008474444039165974</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0001857734896475449</v>
+        <v>0.009336413815617561</v>
       </c>
       <c r="CO13" t="n">
-        <v>4.092902599950321e-05</v>
+        <v>0.01613927073776722</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0005021739052608609</v>
+        <v>0.01936708949506283</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0004123750841245055</v>
+        <v>0.006729850545525551</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0006533853593282402</v>
+        <v>0.01085164956748486</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0005201330641284585</v>
+        <v>0.01025576516985893</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.0002028610906563699</v>
+        <v>0.00382386683486402</v>
       </c>
       <c r="CU13" t="n">
-        <v>6.708471482852474e-05</v>
+        <v>0.009556163102388382</v>
       </c>
       <c r="CV13" t="n">
-        <v>6.87456558807753e-05</v>
+        <v>0.005049952771514654</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0005191437085159123</v>
+        <v>0.01586887799203396</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.0002610209630802274</v>
+        <v>0.0119360564276576</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0002480371040292084</v>
+        <v>0.007182588335126638</v>
       </c>
       <c r="CZ13" t="n">
-        <v>9.062464960152283e-05</v>
+        <v>0.002809731755405664</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0001553999609313905</v>
+        <v>0.01455726847052574</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0001367129443679005</v>
+        <v>0.002405861392617226</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0003230407019145787</v>
+        <v>0.002452540909871459</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.000112114088551607</v>
+        <v>0.004986869171261787</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0003018708666786551</v>
+        <v>0.00360917067155242</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0003049707447644323</v>
+        <v>0.03807497024536133</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.808079418377019e-05</v>
+        <v>0.02266758494079113</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.0008719105389900506</v>
+        <v>0.001074661267921329</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0009093839325942099</v>
+        <v>0.007687154226005077</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.305325662950054e-05</v>
+        <v>0.03080455586314201</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0004137781506869942</v>
+        <v>0.007544977590441704</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0003560693585313857</v>
+        <v>0.01776943355798721</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.0003660070069599897</v>
+        <v>0.003229385009035468</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0001081981608876958</v>
+        <v>0.004472349304705858</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.000274912774330005</v>
+        <v>0.01605900377035141</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0001416729064658284</v>
+        <v>0.004917245823889971</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0002110382192768157</v>
+        <v>0.01677174121141434</v>
       </c>
       <c r="DR13" t="n">
-        <v>4.552314749162178e-06</v>
+        <v>0.0007684105657972395</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0002023520064540207</v>
+        <v>0.01114601641893387</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.0001439207699149847</v>
+        <v>0.008036712184548378</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0001120910819736309</v>
+        <v>0.01505240797996521</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.00012383540160954</v>
+        <v>0.006644466891884804</v>
       </c>
       <c r="DW13" t="n">
-        <v>4.224479926051572e-05</v>
+        <v>0.0002715617883950472</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0001449024566682056</v>
+        <v>0.01155781000852585</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.0002884830464608967</v>
+        <v>0.02409118413925171</v>
       </c>
       <c r="DZ13" t="n">
-        <v>7.438898319378495e-05</v>
+        <v>0.004090375266969204</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0001060160429915413</v>
+        <v>0.009367902763187885</v>
       </c>
       <c r="EB13" t="n">
-        <v>6.763820420019329e-05</v>
+        <v>0.002268383046612144</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0001282463344978169</v>
+        <v>0.01795034296810627</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0001018056354951113</v>
+        <v>0.01012923195958138</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0001919530623126775</v>
+        <v>0.03089181520044804</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0004361521278042346</v>
+        <v>0.0006806562305428088</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0005642212345264852</v>
+        <v>0.001077885273844004</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.0003306689322926104</v>
+        <v>0.0001018457114696503</v>
       </c>
       <c r="EI13" t="n">
-        <v>7.511789590353146e-05</v>
+        <v>0.01810871064662933</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0001903511729324237</v>
+        <v>0.0004199296236038208</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.000105852734122891</v>
+        <v>0.001163813751190901</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0001145355054177344</v>
+        <v>0.00365890096873045</v>
       </c>
       <c r="EM13" t="n">
-        <v>3.380624548299238e-05</v>
+        <v>0.005071666557341814</v>
       </c>
       <c r="EN13" t="n">
-        <v>4.737333802040666e-05</v>
+        <v>0.01649568043649197</v>
       </c>
       <c r="EO13" t="n">
-        <v>5.246871296549216e-05</v>
+        <v>0.003299228148534894</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.0002860706299543381</v>
+        <v>0.01339875534176826</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0003167275863233954</v>
+        <v>0.006188393570482731</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0002332506264792755</v>
+        <v>0.007318482268601656</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.0001458739279769361</v>
+        <v>0.01049218699336052</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0003691407910082489</v>
+        <v>0.015529815107584</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0002723323414102197</v>
+        <v>0.001113223377615213</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0005688680103048682</v>
+        <v>0.0004218935500830412</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0001121197419706732</v>
+        <v>0.002455400535836816</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0001146135327871889</v>
+        <v>0.002335764467716217</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0005014169146306813</v>
+        <v>0.02088550478219986</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.0002099585108226165</v>
+        <v>0.00645759329199791</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0001147465955000371</v>
+        <v>0.008428162895143032</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0001075361506082118</v>
+        <v>0.002474859822541475</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.000107042069430463</v>
+        <v>0.01138986181467772</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0001782741746865213</v>
+        <v>0.002566246781498194</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.0002675191208254546</v>
+        <v>0.0008596227853558958</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0001694470993243158</v>
+        <v>0.007599448785185814</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0001478046469856054</v>
+        <v>0.004024531226605177</v>
       </c>
       <c r="FH13" t="n">
-        <v>2.608927570690867e-05</v>
+        <v>0.004887267481535673</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0004408660461194813</v>
+        <v>0.01388198602944613</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0003196127654518932</v>
+        <v>0.004753808490931988</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0001290650252485648</v>
+        <v>0.003521972335875034</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.0003162331413477659</v>
+        <v>0.01780100911855698</v>
       </c>
       <c r="FM13" t="n">
-        <v>5.560759746003896e-05</v>
+        <v>0.004008694551885128</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0002236477157566696</v>
+        <v>0.01588309183716774</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0001595085632288828</v>
+        <v>0.03426350280642509</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0003796215751208365</v>
+        <v>0.005456761457026005</v>
       </c>
       <c r="FQ13" t="n">
-        <v>6.810799823142588e-05</v>
+        <v>0.01472411304712296</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0005196092533878982</v>
+        <v>0.004778914153575897</v>
       </c>
       <c r="FS13" t="n">
-        <v>8.446753781754524e-05</v>
+        <v>0.008179090917110443</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.0003855727263726294</v>
+        <v>0.00889962911605835</v>
       </c>
       <c r="FU13" t="n">
-        <v>8.950173651101068e-05</v>
+        <v>0.003431764431297779</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0001398304157191887</v>
+        <v>0.002597818151116371</v>
       </c>
       <c r="FW13" t="n">
-        <v>9.741295798448846e-06</v>
+        <v>0.04440363124012947</v>
       </c>
       <c r="FX13" t="n">
-        <v>5.361375951906666e-05</v>
+        <v>0.007331048138439655</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.000457092362921685</v>
+        <v>0.004069864749908447</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0001802322512958199</v>
+        <v>0.003784554777666926</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.000286424474325031</v>
+        <v>0.02825864218175411</v>
       </c>
       <c r="GB13" t="n">
-        <v>7.498521881643683e-06</v>
+        <v>0.00251059653237462</v>
       </c>
       <c r="GC13" t="n">
-        <v>2.330823917873204e-06</v>
+        <v>0.02577867358922958</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0002765968383755535</v>
+        <v>0.01550471782684326</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0006531279068440199</v>
+        <v>0.01126432605087757</v>
       </c>
       <c r="GF13" t="n">
-        <v>8.514353248756379e-05</v>
+        <v>0.004808858036994934</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0003296450304333121</v>
+        <v>0.00198493292555213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.0001067433258867823</v>
+        <v>8.716392885244062e-11</v>
       </c>
       <c r="B14" t="n">
-        <v>0.007076155859977007</v>
+        <v>5.005087455600687e-10</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0007004609215073287</v>
+        <v>1.936589361095642e-10</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001597374328412116</v>
+        <v>2.294964773774666e-10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.002887724200263619</v>
+        <v>7.027427945116571e-11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.002238210057839751</v>
+        <v>4.08947431473905e-10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002263920614495873</v>
+        <v>3.207446114261714e-11</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001012147171422839</v>
+        <v>2.611122151829903e-10</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001946294796653092</v>
+        <v>3.28202021115942e-10</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0004181993426755071</v>
+        <v>1.38052708154035e-10</v>
       </c>
       <c r="K14" t="n">
-        <v>0.005821793805807829</v>
+        <v>5.568677741152328e-10</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0001085758703993633</v>
+        <v>2.040688173998717e-10</v>
       </c>
       <c r="M14" t="n">
-        <v>0.00068520603235811</v>
+        <v>1.87408422114288e-10</v>
       </c>
       <c r="N14" t="n">
-        <v>0.001770576578564942</v>
+        <v>1.307783881188129e-10</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00221057259477675</v>
+        <v>4.036582457178639e-10</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001059163187164813</v>
+        <v>3.143119445270237e-11</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0005012296605855227</v>
+        <v>3.141446547338944e-10</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0005298595642670989</v>
+        <v>1.566594631796647e-10</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001572088804095984</v>
+        <v>1.090578044538049e-10</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0006677579367533326</v>
+        <v>3.943431692299271e-11</v>
       </c>
       <c r="U14" t="n">
-        <v>6.020510045345873e-05</v>
+        <v>5.3821416073907e-11</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0009575799340382218</v>
+        <v>5.716250389697919e-12</v>
       </c>
       <c r="W14" t="n">
-        <v>0.001696154824458063</v>
+        <v>4.744852427629453e-11</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0003103583585470915</v>
+        <v>4.908429565575467e-11</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.698935900814831e-05</v>
+        <v>4.212695470240391e-11</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.001166104571893811</v>
+        <v>8.588102451412283e-11</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.000223777795326896</v>
+        <v>1.199427224207739e-10</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0001957825152203441</v>
+        <v>1.442235567084005e-11</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.937536378856748e-05</v>
+        <v>4.245720788831342e-11</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.470350151881576e-05</v>
+        <v>1.333074484133334e-10</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0001829941902542487</v>
+        <v>9.092880615124699e-11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0004464360245037824</v>
+        <v>7.666819956675397e-11</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0003300041717011482</v>
+        <v>1.319373776897947e-10</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0002685788203962147</v>
+        <v>6.805722652103441e-12</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0002372148737777025</v>
+        <v>1.082628153792342e-10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0008025068091228604</v>
+        <v>2.246705183006625e-10</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.001169228926301003</v>
+        <v>1.247700692763587e-10</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.0004177556838840246</v>
+        <v>2.296019624425938e-11</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0003394566883798689</v>
+        <v>1.037294694583579e-10</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.000401790370233357</v>
+        <v>7.085561304354115e-12</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.0005919424584135413</v>
+        <v>3.935975156910132e-11</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0007315307739190757</v>
+        <v>4.371507496270244e-12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.000103640959423501</v>
+        <v>1.740277887074537e-11</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0002848653239198029</v>
+        <v>9.90295085517845e-12</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.000275433820206672</v>
+        <v>1.030751612535186e-11</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.0001259701530216262</v>
+        <v>2.336337234787322e-10</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.004376392811536789</v>
+        <v>6.15026779504646e-11</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0001126565475715324</v>
+        <v>1.178909470045397e-10</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0007577102514915168</v>
+        <v>6.894013832026147e-11</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.001204310217872262</v>
+        <v>3.567184603259221e-10</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0009558577439747751</v>
+        <v>1.111186420654775e-10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0005670533864758909</v>
+        <v>8.601191980872613e-11</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.883654325269163e-05</v>
+        <v>2.680244914898822e-12</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.0002469075261615217</v>
+        <v>6.621905107584425e-11</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0004677904944401234</v>
+        <v>1.356505741068048e-10</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.001343362382613122</v>
+        <v>3.279075067030846e-10</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.001194936339743435</v>
+        <v>8.954671726346675e-11</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.129917265847325e-05</v>
+        <v>1.423614004458784e-10</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.001948863849975169</v>
+        <v>3.974320317290392e-10</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0007001645280979574</v>
+        <v>9.298942865720861e-11</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0007471985882148147</v>
+        <v>4.23922563719259e-11</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.0003473926044534892</v>
+        <v>1.158900753139847e-10</v>
       </c>
       <c r="BK14" t="n">
-        <v>2.368917921558022e-05</v>
+        <v>3.766054412768227e-10</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.000706191174685955</v>
+        <v>4.460010832874062e-11</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001105072209611535</v>
+        <v>1.165740004527294e-10</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0007590333116240799</v>
+        <v>1.633219774699324e-11</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0003013625682797283</v>
+        <v>7.034093446600664e-11</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.001327592064626515</v>
+        <v>5.130173022505069e-11</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.00087694451212883</v>
+        <v>6.585611223020038e-11</v>
       </c>
       <c r="BR14" t="n">
-        <v>8.625432383269072e-05</v>
+        <v>6.891886367155209e-11</v>
       </c>
       <c r="BS14" t="n">
-        <v>6.322131957858801e-05</v>
+        <v>4.703582662246575e-11</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.0002021242398768663</v>
+        <v>7.340690555412976e-11</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0001237425021827221</v>
+        <v>1.959388762351466e-10</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.002795739565044641</v>
+        <v>2.827677154926267e-11</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.00088053586659953</v>
+        <v>1.878137229072152e-11</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.0002990506472997367</v>
+        <v>2.64530897187143e-11</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.00068224489223212</v>
+        <v>4.11524044008349e-11</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0001597133814357221</v>
+        <v>4.895157196260769e-12</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0002920205588452518</v>
+        <v>6.296634763071352e-13</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0002792218001559377</v>
+        <v>3.491290243018419e-11</v>
       </c>
       <c r="CC14" t="n">
-        <v>5.94313933106605e-05</v>
+        <v>3.753885396973189e-11</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0001776761637302116</v>
+        <v>3.583237873083789e-11</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.001237953314557672</v>
+        <v>1.052766207543243e-10</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0003919405862689018</v>
+        <v>1.959119498573525e-11</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0002757798356469721</v>
+        <v>5.533874747332135e-11</v>
       </c>
       <c r="CH14" t="n">
-        <v>2.009022682614159e-05</v>
+        <v>6.461844948013606e-11</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.0004029963747598231</v>
+        <v>1.135297897358889e-10</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0004567473370116204</v>
+        <v>1.811021818620695e-11</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0002669994137249887</v>
+        <v>3.07201729332629e-11</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0002092139038722962</v>
+        <v>4.617215637603422e-11</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.001706832554191351</v>
+        <v>2.861939157883242e-11</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0005522657302208245</v>
+        <v>1.19522447494802e-10</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0001995486090891063</v>
+        <v>1.388572867799809e-10</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0004767300561070442</v>
+        <v>2.421974773514357e-11</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0008239275775849819</v>
+        <v>1.333958915550326e-10</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0007874335278756917</v>
+        <v>4.05566760730558e-11</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.001400968641974032</v>
+        <v>3.980328566743907e-11</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.000858025683555752</v>
+        <v>5.020507967690158e-11</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0005387012497521937</v>
+        <v>1.51230597489338e-10</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0001419264008291066</v>
+        <v>5.517870535487468e-11</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.001148282084614038</v>
+        <v>1.106810545992154e-10</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0005424651317298412</v>
+        <v>2.31491908975201e-11</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.000543569796718657</v>
+        <v>5.656740353909839e-11</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.000103051817859523</v>
+        <v>2.526455607221312e-11</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.0005587932537309825</v>
+        <v>1.212638878200778e-10</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0003489457303658128</v>
+        <v>1.615422726142235e-11</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0005804660613648593</v>
+        <v>5.799452584831499e-11</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0001059769201674499</v>
+        <v>6.152844206352981e-11</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.0006361289997585118</v>
+        <v>6.405258268227243e-12</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.001413789112120867</v>
+        <v>2.265889559316392e-10</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.0001423817011527717</v>
+        <v>2.228058015862899e-10</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.001987298484891653</v>
+        <v>9.972094677790366e-11</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001991472207009792</v>
+        <v>6.744635405731003e-11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.0004691737412940711</v>
+        <v>3.112343369138237e-11</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.0005687807570211589</v>
+        <v>1.251580783456774e-10</v>
       </c>
       <c r="DL14" t="n">
-        <v>7.487759285140783e-05</v>
+        <v>3.186717556502572e-11</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.001065071439370513</v>
+        <v>3.920436024429375e-12</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.00036878656828776</v>
+        <v>1.397192361807242e-10</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.0003982394118793309</v>
+        <v>1.202608568284802e-10</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0008304739603772759</v>
+        <v>1.074114928945047e-11</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0004876785387750715</v>
+        <v>1.302023072691227e-10</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.001229006564244628</v>
+        <v>7.874761953630127e-11</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.000180155344423838</v>
+        <v>4.769026493156581e-11</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0004756523994728923</v>
+        <v>1.236988983466247e-10</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0004430365806911141</v>
+        <v>3.696850464640633e-11</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.0001607160666026175</v>
+        <v>1.334442001343916e-10</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0001814879360608757</v>
+        <v>7.594944811950555e-11</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0002928546164184809</v>
+        <v>4.394820618536244e-11</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0005114999366924167</v>
+        <v>1.020803441775797e-10</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0001021116913761944</v>
+        <v>1.080653969087741e-11</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0004336941055953503</v>
+        <v>2.571689805552779e-10</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0006701651145704091</v>
+        <v>8.442892218685216e-11</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.0002504111616872251</v>
+        <v>1.991880688168024e-10</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0002640444727148861</v>
+        <v>2.611938963725802e-11</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0002165943442378193</v>
+        <v>1.725533604890472e-11</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.000743845768738538</v>
+        <v>1.519170032826533e-11</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.001394948340021074</v>
+        <v>9.324112315578503e-11</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.000481476541608572</v>
+        <v>3.633725959018008e-11</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.0004415916046127677</v>
+        <v>3.258747438561471e-11</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.0002976586984004825</v>
+        <v>1.406458283170764e-12</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.0001935889013111591</v>
+        <v>5.883278586527041e-11</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0003621482173912227</v>
+        <v>4.901028888282255e-11</v>
       </c>
       <c r="EM14" t="n">
-        <v>3.08304006466642e-05</v>
+        <v>3.927648137280748e-11</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0002056996163446456</v>
+        <v>5.85470283365197e-11</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0002734742010943592</v>
+        <v>5.313893769454126e-11</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.0003736304934136569</v>
+        <v>1.336306065802262e-10</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0003731258038897067</v>
+        <v>1.920757650153426e-11</v>
       </c>
       <c r="ER14" t="n">
-        <v>9.215198224410415e-05</v>
+        <v>1.949295586056721e-11</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.0001568481529830024</v>
+        <v>1.143515074297774e-10</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.0005661356844939291</v>
+        <v>9.88403317525588e-11</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0002882122062146664</v>
+        <v>1.337130753342741e-11</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0009198447223752737</v>
+        <v>4.35471450566105e-11</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0007931620348244905</v>
+        <v>3.782252636086447e-11</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0002520371344871819</v>
+        <v>3.989753666333584e-11</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.0009462156449444592</v>
+        <v>1.286862144622702e-10</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0003151189011987299</v>
+        <v>2.120770573044162e-11</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0002121741708833724</v>
+        <v>6.663002094509096e-11</v>
       </c>
       <c r="FB14" t="n">
-        <v>7.624008503626101e-06</v>
+        <v>5.411702683200126e-11</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.0004785270139109343</v>
+        <v>1.112911360290347e-10</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.0003792969800997525</v>
+        <v>1.778698022203429e-11</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0003082916664425284</v>
+        <v>7.769537790913716e-11</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0002225496427854523</v>
+        <v>2.952255107047108e-11</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0002720982884056866</v>
+        <v>2.418804392889662e-11</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.0003652569430414587</v>
+        <v>3.201337805958104e-11</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0008706278749741614</v>
+        <v>1.76267375695538e-10</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.001404790673404932</v>
+        <v>2.960506839677635e-12</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.0008596863481216133</v>
+        <v>1.621045242483632e-10</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0004102512320969254</v>
+        <v>8.606401008526277e-11</v>
       </c>
       <c r="FM14" t="n">
-        <v>7.064882811391726e-05</v>
+        <v>3.064996173529622e-11</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0002839239314198494</v>
+        <v>1.177763025994594e-10</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0006253012106753886</v>
+        <v>8.718545330133054e-11</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.001122743939049542</v>
+        <v>9.789317967356936e-11</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.001026294659823179</v>
+        <v>2.705456692009278e-10</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.001043280586600304</v>
+        <v>2.950119593059242e-10</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0004348165239207447</v>
+        <v>1.556145212688875e-10</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0001089222205337137</v>
+        <v>6.23941801003447e-11</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0005099669797345996</v>
+        <v>3.91221881279602e-11</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0003644735843408853</v>
+        <v>1.004335364873654e-10</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0005542145227082074</v>
+        <v>1.400514149096921e-10</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0002208577643614262</v>
+        <v>1.064361307423489e-10</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.000963082246016711</v>
+        <v>9.826799096668282e-12</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0003853582602459937</v>
+        <v>9.431576353247095e-11</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0003584529040381312</v>
+        <v>1.562839302415853e-10</v>
       </c>
       <c r="GB14" t="n">
-        <v>4.916064790450037e-05</v>
+        <v>1.281735273472862e-10</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.0002707565727178007</v>
+        <v>2.232424800574506e-10</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.0001187199959531426</v>
+        <v>1.324419462989113e-10</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.0009804046712815762</v>
+        <v>5.127437363583454e-11</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0002486290468368679</v>
+        <v>6.430792010014841e-11</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.0005649521481245756</v>
+        <v>4.738957143368694e-11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2.344127460673917e-05</v>
+        <v>0.0006100183818489313</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001328091369941831</v>
+        <v>0.01091083697974682</v>
       </c>
       <c r="C15" t="n">
-        <v>6.128921086201444e-05</v>
+        <v>0.001524569466710091</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0008389499271288514</v>
+        <v>0.008385840803384781</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0001508982386440039</v>
+        <v>0.0002864844864234328</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0001038473928929307</v>
+        <v>0.01651126146316528</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001438175968360156</v>
+        <v>0.00449798908084631</v>
       </c>
       <c r="H15" t="n">
-        <v>5.118723856867291e-05</v>
+        <v>0.003825858002528548</v>
       </c>
       <c r="I15" t="n">
-        <v>6.998040771577507e-05</v>
+        <v>0.003233078401535749</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0001096649721148424</v>
+        <v>0.0009500945452600718</v>
       </c>
       <c r="K15" t="n">
-        <v>0.001176471821963787</v>
+        <v>0.01188022922724485</v>
       </c>
       <c r="L15" t="n">
-        <v>2.262325688207056e-05</v>
+        <v>0.003298849798738956</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0007797848666086793</v>
+        <v>0.01084455288946629</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0002163079043384641</v>
+        <v>0.006161552388221025</v>
       </c>
       <c r="O15" t="n">
-        <v>2.804513860610314e-05</v>
+        <v>0.01742514409124851</v>
       </c>
       <c r="P15" t="n">
-        <v>9.569689427735284e-05</v>
+        <v>0.002566105686128139</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0001713107485556975</v>
+        <v>0.003463425906375051</v>
       </c>
       <c r="R15" t="n">
-        <v>4.482961685425835e-06</v>
+        <v>0.001110986224375665</v>
       </c>
       <c r="S15" t="n">
-        <v>9.173302532872185e-05</v>
+        <v>0.0006279018125496805</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0001531977322883904</v>
+        <v>7.240826380439103e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32631548694917e-05</v>
+        <v>0.0008678201120346785</v>
       </c>
       <c r="V15" t="n">
-        <v>8.488398452755064e-05</v>
+        <v>0.001385683426633477</v>
       </c>
       <c r="W15" t="n">
-        <v>9.259504440706223e-05</v>
+        <v>0.0001218564866576344</v>
       </c>
       <c r="X15" t="n">
-        <v>2.942816900031175e-05</v>
+        <v>0.002910948824137449</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.000125891572679393</v>
+        <v>0.001701288972981274</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.819824481382966e-05</v>
+        <v>0.001699293032288551</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0001124939590226859</v>
+        <v>0.0007867134409025311</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.0001294009998673573</v>
+        <v>0.001491115195676684</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.0002637296274770051</v>
+        <v>0.0008423482067883015</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.92080933629768e-05</v>
+        <v>0.00295474543236196</v>
       </c>
       <c r="AE15" t="n">
-        <v>3.256238051108085e-05</v>
+        <v>0.00180895603261888</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.530262983986177e-05</v>
+        <v>0.001744106644764543</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.880510510294698e-05</v>
+        <v>0.005263583734631538</v>
       </c>
       <c r="AH15" t="n">
-        <v>8.379103383049369e-05</v>
+        <v>0.0006852652295492589</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.15216314245481e-05</v>
+        <v>0.006317395716905594</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.871685086982325e-05</v>
+        <v>2.482417039573193e-05</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.491475217742845e-05</v>
+        <v>0.001908076461404562</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0001298873248742893</v>
+        <v>0.00258596520870924</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.673570477578323e-05</v>
+        <v>0.001739586936309934</v>
       </c>
       <c r="AN15" t="n">
-        <v>3.810768248513341e-05</v>
+        <v>0.001193506643176079</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.0001145831265603192</v>
+        <v>0.0009234725730493665</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.335467282449827e-05</v>
+        <v>0.0006565444055013359</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.967342339223251e-05</v>
+        <v>0.000558718922547996</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.135981751256622e-05</v>
+        <v>0.0008715587900951505</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.715107595780864e-05</v>
+        <v>0.001669940887950361</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0001380734611302614</v>
+        <v>0.001071009435690939</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.000812740414403379</v>
+        <v>0.00533048901706934</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.0001804017229005694</v>
+        <v>0.003466112306341529</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.0002628506335895509</v>
+        <v>0.002601916203275323</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.645934702944942e-05</v>
+        <v>0.01119010616093874</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.939955296227708e-05</v>
+        <v>0.008567022159695625</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.427600313443691e-05</v>
+        <v>0.0006463570753112435</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.828615394420922e-05</v>
+        <v>0.001753930933773518</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.146221570204943e-05</v>
+        <v>0.0001690496865194291</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.795029574073851e-05</v>
+        <v>0.0001515529584139585</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.000190411796211265</v>
+        <v>0.002625121036544442</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0002286593371536583</v>
+        <v>0.002656916156411171</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.0001493773597758263</v>
+        <v>0.002514716470614076</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.0001349251542706043</v>
+        <v>0.004754030611366034</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.109198612743057e-05</v>
+        <v>0.004314529709517956</v>
       </c>
       <c r="BI15" t="n">
-        <v>8.687474473845214e-05</v>
+        <v>0.001392926089465618</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.0001662664290051907</v>
+        <v>0.004062519408762455</v>
       </c>
       <c r="BK15" t="n">
-        <v>3.818958066403866e-05</v>
+        <v>0.0007917088805697858</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0001138553707278334</v>
+        <v>3.794189251493663e-05</v>
       </c>
       <c r="BM15" t="n">
-        <v>5.291876732371747e-05</v>
+        <v>0.0009185783565044403</v>
       </c>
       <c r="BN15" t="n">
-        <v>9.118855086853728e-05</v>
+        <v>7.888844993431121e-05</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.500182330957614e-05</v>
+        <v>0.003398865228518844</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0002101925056194887</v>
+        <v>0.0003987842646893114</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.977500505745411e-05</v>
+        <v>0.00214948202483356</v>
       </c>
       <c r="BR15" t="n">
-        <v>4.498177077039145e-05</v>
+        <v>0.0008323094225488603</v>
       </c>
       <c r="BS15" t="n">
-        <v>6.201679207151756e-05</v>
+        <v>0.001715496531687677</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.0001014241279335693</v>
+        <v>0.002456757472828031</v>
       </c>
       <c r="BU15" t="n">
-        <v>9.863698505796492e-05</v>
+        <v>0.000612282135989517</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.0004223456780891865</v>
+        <v>0.003655679989606142</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.0001032101281452924</v>
+        <v>0.0009283952531404793</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.0001803256309358403</v>
+        <v>0.003166347974911332</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.10851197456941e-05</v>
+        <v>0.002537505235522985</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1.753843025653623e-05</v>
+        <v>0.004343654494732618</v>
       </c>
       <c r="CA15" t="n">
-        <v>6.130558176664636e-05</v>
+        <v>0.002575437072664499</v>
       </c>
       <c r="CB15" t="n">
-        <v>1.379690183966886e-05</v>
+        <v>0.001470320392400026</v>
       </c>
       <c r="CC15" t="n">
-        <v>8.069753675954416e-05</v>
+        <v>0.001736127189360559</v>
       </c>
       <c r="CD15" t="n">
-        <v>2.206543103966396e-05</v>
+        <v>0.000813117774669081</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0002257539017591625</v>
+        <v>0.003161991946399212</v>
       </c>
       <c r="CF15" t="n">
-        <v>5.274216891848482e-05</v>
+        <v>0.0004634566430468112</v>
       </c>
       <c r="CG15" t="n">
-        <v>9.662334196036682e-05</v>
+        <v>0.002712369430810213</v>
       </c>
       <c r="CH15" t="n">
-        <v>4.777904541697353e-05</v>
+        <v>9.712908649817109e-05</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.520065754652023e-05</v>
+        <v>0.003936037886887789</v>
       </c>
       <c r="CJ15" t="n">
-        <v>3.430507786106318e-05</v>
+        <v>3.060235758312047e-05</v>
       </c>
       <c r="CK15" t="n">
-        <v>6.297632353380322e-06</v>
+        <v>0.001347665558569133</v>
       </c>
       <c r="CL15" t="n">
-        <v>3.048580947506707e-05</v>
+        <v>0.002164967823773623</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.0002997091214638203</v>
+        <v>0.002040326595306396</v>
       </c>
       <c r="CN15" t="n">
-        <v>5.648618389386684e-05</v>
+        <v>0.001135824946686625</v>
       </c>
       <c r="CO15" t="n">
-        <v>2.532245707698166e-05</v>
+        <v>0.004744160920381546</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.0002095800591632724</v>
+        <v>0.003757256548851728</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0002458445669617504</v>
+        <v>0.004489569924771786</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.0001402459020027891</v>
+        <v>0.001635625609196723</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.0001560426462674513</v>
+        <v>0.0007812828989699483</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0002114918170263991</v>
+        <v>0.001180523540824652</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.136297032644507e-05</v>
+        <v>0.001869541476480663</v>
       </c>
       <c r="CV15" t="n">
-        <v>4.606332367984578e-06</v>
+        <v>0.0009981765178963542</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.0002285990049131215</v>
+        <v>0.003210892667993903</v>
       </c>
       <c r="CX15" t="n">
-        <v>9.073043474927545e-05</v>
+        <v>0.0006978639867156744</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.0001376866566715762</v>
+        <v>0.00308678112924099</v>
       </c>
       <c r="CZ15" t="n">
-        <v>5.111555947223678e-05</v>
+        <v>0.001153879915364087</v>
       </c>
       <c r="DA15" t="n">
-        <v>3.635254188338877e-06</v>
+        <v>0.004424796439707279</v>
       </c>
       <c r="DB15" t="n">
-        <v>4.249337143846788e-05</v>
+        <v>0.0004150564200244844</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.241001129732467e-05</v>
+        <v>0.001416829065419734</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.083668485080125e-05</v>
+        <v>0.001701465458609164</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.0001778237783582881</v>
+        <v>0.002565657487139106</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.0001176974474219605</v>
+        <v>0.004586771130561829</v>
       </c>
       <c r="DG15" t="n">
-        <v>8.598794011049904e-06</v>
+        <v>0.002700846409425139</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.0002702996134757996</v>
+        <v>0.002270934637635946</v>
       </c>
       <c r="DI15" t="n">
-        <v>8.441562385996804e-05</v>
+        <v>0.002622174331918359</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.407956319279037e-05</v>
+        <v>0.005540479440242052</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.392130697146058e-05</v>
+        <v>0.001022060168907046</v>
       </c>
       <c r="DL15" t="n">
-        <v>8.097907266346738e-05</v>
+        <v>0.00243698013946414</v>
       </c>
       <c r="DM15" t="n">
-        <v>4.465288293431513e-05</v>
+        <v>0.002314375014975667</v>
       </c>
       <c r="DN15" t="n">
-        <v>3.535300129442476e-05</v>
+        <v>0.002254260238260031</v>
       </c>
       <c r="DO15" t="n">
-        <v>9.395166125614196e-05</v>
+        <v>0.002933249343186617</v>
       </c>
       <c r="DP15" t="n">
-        <v>6.731241592206061e-05</v>
+        <v>0.0008147505577653646</v>
       </c>
       <c r="DQ15" t="n">
-        <v>7.668549369554967e-05</v>
+        <v>0.001433533616364002</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.000170166531461291</v>
+        <v>0.001107725081965327</v>
       </c>
       <c r="DS15" t="n">
-        <v>9.233554919774178e-06</v>
+        <v>0.0006979901227168739</v>
       </c>
       <c r="DT15" t="n">
-        <v>1.778655132511631e-05</v>
+        <v>0.00161945668514818</v>
       </c>
       <c r="DU15" t="n">
-        <v>6.042074528522789e-05</v>
+        <v>0.002496315399184823</v>
       </c>
       <c r="DV15" t="n">
-        <v>6.561248301295564e-05</v>
+        <v>0.001849757158197463</v>
       </c>
       <c r="DW15" t="n">
-        <v>8.48652925924398e-05</v>
+        <v>0.001404210226610303</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.0001930511207319796</v>
+        <v>4.358208389021456e-05</v>
       </c>
       <c r="DY15" t="n">
-        <v>2.160745862056501e-05</v>
+        <v>0.004443435929715633</v>
       </c>
       <c r="DZ15" t="n">
-        <v>8.740303746890277e-05</v>
+        <v>0.00066191959194839</v>
       </c>
       <c r="EA15" t="n">
-        <v>8.29832351882942e-05</v>
+        <v>0.002771639497950673</v>
       </c>
       <c r="EB15" t="n">
-        <v>3.410944918869063e-05</v>
+        <v>0.001174969831481576</v>
       </c>
       <c r="EC15" t="n">
-        <v>5.843611143063754e-05</v>
+        <v>0.0007019853219389915</v>
       </c>
       <c r="ED15" t="n">
-        <v>1.422476634616032e-05</v>
+        <v>0.003428001422435045</v>
       </c>
       <c r="EE15" t="n">
-        <v>1.448685725335963e-05</v>
+        <v>0.002699586329981685</v>
       </c>
       <c r="EF15" t="n">
-        <v>2.959371704491787e-05</v>
+        <v>0.001268021413125098</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.0001647202298045158</v>
+        <v>0.001454539597034454</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0001079536596080288</v>
+        <v>0.002677328651770949</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.000149735642480664</v>
+        <v>0.001376492902636528</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0001759344595484436</v>
+        <v>0.002188990823924541</v>
       </c>
       <c r="EK15" t="n">
-        <v>3.963958988606464e-06</v>
+        <v>0.002713405061513186</v>
       </c>
       <c r="EL15" t="n">
-        <v>3.365690645296127e-05</v>
+        <v>0.0008099759579636157</v>
       </c>
       <c r="EM15" t="n">
-        <v>4.575281127472408e-05</v>
+        <v>0.0007922837976366282</v>
       </c>
       <c r="EN15" t="n">
-        <v>2.054047763522249e-05</v>
+        <v>0.001189526286907494</v>
       </c>
       <c r="EO15" t="n">
-        <v>4.493533197091892e-06</v>
+        <v>0.0004646496963687241</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.0002600492734927684</v>
+        <v>0.001677930820733309</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.0001243182632606477</v>
+        <v>0.001608246588148177</v>
       </c>
       <c r="ER15" t="n">
-        <v>8.932036143960431e-05</v>
+        <v>0.001749685732647777</v>
       </c>
       <c r="ES15" t="n">
-        <v>4.548985816654749e-05</v>
+        <v>0.001365101663395762</v>
       </c>
       <c r="ET15" t="n">
-        <v>3.099498280789703e-05</v>
+        <v>0.0005434049526229501</v>
       </c>
       <c r="EU15" t="n">
-        <v>9.917736315401271e-05</v>
+        <v>0.0007210102630779147</v>
       </c>
       <c r="EV15" t="n">
-        <v>6.117893644841388e-05</v>
+        <v>0.001861009281128645</v>
       </c>
       <c r="EW15" t="n">
-        <v>4.849999822909012e-05</v>
+        <v>0.002360180485993624</v>
       </c>
       <c r="EX15" t="n">
-        <v>4.638891914510168e-05</v>
+        <v>0.001075776759535074</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.0002385802363278344</v>
+        <v>0.003931595478206873</v>
       </c>
       <c r="EZ15" t="n">
-        <v>6.22990119154565e-05</v>
+        <v>0.0002487122546881437</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0001126578063121997</v>
+        <v>0.003488816320896149</v>
       </c>
       <c r="FB15" t="n">
-        <v>3.180188286933117e-05</v>
+        <v>0.0002208839432569221</v>
       </c>
       <c r="FC15" t="n">
-        <v>2.032387101280619e-06</v>
+        <v>0.003548319218680263</v>
       </c>
       <c r="FD15" t="n">
-        <v>3.404651943128556e-05</v>
+        <v>8.539532427676022e-05</v>
       </c>
       <c r="FE15" t="n">
-        <v>3.446220034675207e-06</v>
+        <v>0.001194167765788734</v>
       </c>
       <c r="FF15" t="n">
-        <v>2.569826756371185e-05</v>
+        <v>0.0009770996402949095</v>
       </c>
       <c r="FG15" t="n">
-        <v>3.297924195067026e-05</v>
+        <v>0.0004393582639750093</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0001190610346384346</v>
+        <v>0.002994931302964687</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.0001055760076269507</v>
+        <v>0.004009094089269638</v>
       </c>
       <c r="FJ15" t="n">
-        <v>9.157926979241893e-05</v>
+        <v>0.003745348192751408</v>
       </c>
       <c r="FK15" t="n">
-        <v>9.016247349791229e-05</v>
+        <v>0.001052878680638969</v>
       </c>
       <c r="FL15" t="n">
-        <v>5.653986227116548e-05</v>
+        <v>0.005897665396332741</v>
       </c>
       <c r="FM15" t="n">
-        <v>3.763478889595717e-05</v>
+        <v>6.846096221124753e-05</v>
       </c>
       <c r="FN15" t="n">
-        <v>3.842043952317908e-05</v>
+        <v>0.002820300869643688</v>
       </c>
       <c r="FO15" t="n">
-        <v>3.024628131242935e-05</v>
+        <v>0.004323304165154696</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.0001426338421879336</v>
+        <v>0.002394827781245112</v>
       </c>
       <c r="FQ15" t="n">
-        <v>6.513920379802585e-05</v>
+        <v>0.001476940116845071</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.0001864634832600132</v>
+        <v>0.00746831251308322</v>
       </c>
       <c r="FS15" t="n">
-        <v>2.194781700382009e-06</v>
+        <v>0.002728550229221582</v>
       </c>
       <c r="FT15" t="n">
-        <v>1.47415939864004e-05</v>
+        <v>0.003439413150772452</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.0001179099344881251</v>
+        <v>0.002928270027041435</v>
       </c>
       <c r="FV15" t="n">
-        <v>2.768711055978201e-05</v>
+        <v>0.001219171099364758</v>
       </c>
       <c r="FW15" t="n">
-        <v>5.123337905388325e-05</v>
+        <v>0.003186206333339214</v>
       </c>
       <c r="FX15" t="n">
-        <v>6.469209620263427e-05</v>
+        <v>0.002587867900729179</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.0001239363627973944</v>
+        <v>7.845996879041195e-05</v>
       </c>
       <c r="FZ15" t="n">
-        <v>2.673271228559315e-05</v>
+        <v>0.001928976736962795</v>
       </c>
       <c r="GA15" t="n">
-        <v>6.715555355185643e-05</v>
+        <v>0.00337348273023963</v>
       </c>
       <c r="GB15" t="n">
-        <v>4.551983874989673e-05</v>
+        <v>0.001572297420352697</v>
       </c>
       <c r="GC15" t="n">
-        <v>1.505506497778697e-05</v>
+        <v>0.007691221311688423</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.0001490558934165165</v>
+        <v>0.0072904615662992</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.0002539316774345934</v>
+        <v>0.0007823075284250081</v>
       </c>
       <c r="GF15" t="n">
-        <v>3.911600651917979e-05</v>
+        <v>0.001204625703394413</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.0001031742358463816</v>
+        <v>0.0008006924763321877</v>
       </c>
     </row>
     <row r="16">
@@ -9534,571 +9534,571 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.0001151496253442019</v>
+        <v>0.0238603875041008</v>
       </c>
       <c r="B17" t="n">
-        <v>0.003772437805309892</v>
+        <v>0.3278186321258545</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0001351825776509941</v>
+        <v>0.08757694810628891</v>
       </c>
       <c r="D17" t="n">
-        <v>0.001087681506760418</v>
+        <v>0.2153580188751221</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0008930174517445266</v>
+        <v>0.1641803681850433</v>
       </c>
       <c r="F17" t="n">
-        <v>0.001566610764712095</v>
+        <v>0.3914581537246704</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004269697237759829</v>
+        <v>0.1182466670870781</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001181790372356772</v>
+        <v>0.1430990248918533</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0006145432125777006</v>
+        <v>0.1122113987803459</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0006506874924525619</v>
+        <v>0.01336544938385487</v>
       </c>
       <c r="K17" t="n">
-        <v>0.003261170582845807</v>
+        <v>0.5470540523529053</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0003018025308847427</v>
+        <v>0.00881006196141243</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0006443498423323035</v>
+        <v>0.3060681819915771</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0004051151918247342</v>
+        <v>0.0875752866268158</v>
       </c>
       <c r="O17" t="n">
-        <v>0.002052780706435442</v>
+        <v>0.3669158220291138</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0003552342823240906</v>
+        <v>0.2152404636144638</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.41065863519907e-05</v>
+        <v>0.0493684895336628</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0007623311830684543</v>
+        <v>0.01713394001126289</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0002460376126691699</v>
+        <v>0.06503435969352722</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0004642634594347328</v>
+        <v>0.01804506219923496</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0003559053875505924</v>
+        <v>0.02925712801516056</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0003002985031343997</v>
+        <v>0.1740189492702484</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0004784594348166138</v>
+        <v>0.1600643545389175</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0003236875054426491</v>
+        <v>0.1440500766038895</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0001798303856048733</v>
+        <v>0.07102765142917633</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0008727470994926989</v>
+        <v>0.05700059980154037</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0005187537171877921</v>
+        <v>0.05150894820690155</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0003106345247942954</v>
+        <v>0.0491805337369442</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0001413928403053433</v>
+        <v>0.02432439848780632</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0002710857952479273</v>
+        <v>0.07273381948471069</v>
       </c>
       <c r="AE17" t="n">
-        <v>9.307905565947294e-05</v>
+        <v>0.1428353786468506</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.0003978085587732494</v>
+        <v>0.1895049214363098</v>
       </c>
       <c r="AG17" t="n">
-        <v>7.141115929698572e-05</v>
+        <v>0.09260742366313934</v>
       </c>
       <c r="AH17" t="n">
-        <v>6.674912583548576e-05</v>
+        <v>0.02285607717931271</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0004482378717511892</v>
+        <v>0.1884015798568726</v>
       </c>
       <c r="AJ17" t="n">
-        <v>8.824552787700668e-05</v>
+        <v>0.01065931841731071</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0004547509597614408</v>
+        <v>0.06983904540538788</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.0007177432416938245</v>
+        <v>0.1020763292908669</v>
       </c>
       <c r="AM17" t="n">
-        <v>6.121543265180662e-05</v>
+        <v>0.03302278369665146</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.000134811969473958</v>
+        <v>0.1123791188001633</v>
       </c>
       <c r="AO17" t="n">
-        <v>7.751772500341758e-05</v>
+        <v>0.02854068763554096</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.0004307539202272892</v>
+        <v>0.07439987361431122</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0002377799537498504</v>
+        <v>0.05212863907217979</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0002185553166782483</v>
+        <v>0.0759558379650116</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0004911798750981688</v>
+        <v>0.05988448858261108</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.000422948447521776</v>
+        <v>0.07114406675100327</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.002564182272180915</v>
+        <v>0.6237984299659729</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.0005978688132017851</v>
+        <v>0.0363069660961628</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.0004248520126566291</v>
+        <v>0.1613843142986298</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.0002724712830968201</v>
+        <v>0.05820874124765396</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.0009239607024937868</v>
+        <v>0.1192106530070305</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0008281497284770012</v>
+        <v>0.08051973581314087</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0005655442946590483</v>
+        <v>0.1211066022515297</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.0007656764355488122</v>
+        <v>0.04132017493247986</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.722480662167072e-05</v>
+        <v>0.06663972139358521</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0006634785095229745</v>
+        <v>0.1433097571134567</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.0009161152993328869</v>
+        <v>0.007593549787998199</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.0003292430774308741</v>
+        <v>0.009958097711205482</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.0002752863219939172</v>
+        <v>0.01746609807014465</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0006119519821368158</v>
+        <v>0.114616684615612</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0002713205758482218</v>
+        <v>0.1041639372706413</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.0005119545385241508</v>
+        <v>0.1547438353300095</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.0004854003782384098</v>
+        <v>0.1062359884381294</v>
       </c>
       <c r="BL17" t="n">
-        <v>6.478576688095927e-05</v>
+        <v>0.1039485186338425</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.0002602734311949462</v>
+        <v>0.1247590184211731</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.0003750416217371821</v>
+        <v>0.02858735620975494</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.013456833083183e-05</v>
+        <v>0.0204508863389492</v>
       </c>
       <c r="BP17" t="n">
-        <v>1.528987922938541e-05</v>
+        <v>0.04662137478590012</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0002303438232047483</v>
+        <v>0.06499665230512619</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.0005132809747010469</v>
+        <v>0.1424636989831924</v>
       </c>
       <c r="BS17" t="n">
-        <v>3.877762355841696e-05</v>
+        <v>0.004655491095036268</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0001831257686717436</v>
+        <v>0.004270582925528288</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.00012286810670048</v>
+        <v>0.03152813017368317</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.001460571074858308</v>
+        <v>0.2506852447986603</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.0004067076661158353</v>
+        <v>0.0525679774582386</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.0001038012560456991</v>
+        <v>0.1875133514404297</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0002860353561118245</v>
+        <v>0.06979868561029434</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.0004235917876940221</v>
+        <v>0.2177310436964035</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.972734753508121e-05</v>
+        <v>0.05761794000864029</v>
       </c>
       <c r="CB17" t="n">
-        <v>6.472696259152144e-05</v>
+        <v>0.02555078268051147</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.0005436238716356456</v>
+        <v>0.01094912923872471</v>
       </c>
       <c r="CD17" t="n">
-        <v>7.420816109515727e-05</v>
+        <v>0.03024893254041672</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.0006691511953249574</v>
+        <v>0.1087657287716866</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.0003441630105953664</v>
+        <v>0.03056925907731056</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0002112838556058705</v>
+        <v>0.0260018315166235</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0001135615311795846</v>
+        <v>0.01083933934569359</v>
       </c>
       <c r="CI17" t="n">
-        <v>7.164439011830837e-05</v>
+        <v>0.08117788285017014</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.0002825236297212541</v>
+        <v>0.004946682136505842</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0001236338866874576</v>
+        <v>0.0511358305811882</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.0003821926366072148</v>
+        <v>0.04450191929936409</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.0007380431052297354</v>
+        <v>0.06669295579195023</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0004939188365824521</v>
+        <v>0.2007817476987839</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0001735168480081484</v>
+        <v>0.04999972879886627</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.0009157379390671849</v>
+        <v>0.08737646788358688</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0007024257211014628</v>
+        <v>0.1378830671310425</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.0004285740724299103</v>
+        <v>0.07499115914106369</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.0007912650471553206</v>
+        <v>0.03803486377000809</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0006703606341034174</v>
+        <v>0.01599886268377304</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0001078164859791286</v>
+        <v>0.07919241487979889</v>
       </c>
       <c r="CV17" t="n">
-        <v>8.276832522824407e-05</v>
+        <v>0.06798443198204041</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0005652924883179367</v>
+        <v>0.09648110717535019</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.0003565567312762141</v>
+        <v>0.0410093180835247</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0004459036572370678</v>
+        <v>0.04080470651388168</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0001937971828738227</v>
+        <v>0.01390300877392292</v>
       </c>
       <c r="DA17" t="n">
-        <v>6.154440779937431e-05</v>
+        <v>0.1020304933190346</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0003019938594661653</v>
+        <v>0.009020258672535419</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0002685005019884557</v>
+        <v>0.03266804292798042</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.0003165269445162266</v>
+        <v>0.0486549437046051</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.0003667623095680028</v>
+        <v>0.01667216792702675</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0004603150300681591</v>
+        <v>0.05013393610715866</v>
       </c>
       <c r="DG17" t="n">
-        <v>7.528477726737037e-05</v>
+        <v>0.1779147535562515</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.001380494795739651</v>
+        <v>0.03673830255866051</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.001086712814867496</v>
+        <v>0.1649557203054428</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.001270108507014811</v>
+        <v>0.08268347382545471</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.0003124093636870384</v>
+        <v>0.02521047741174698</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0005809690337628126</v>
+        <v>0.02966951765120029</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0006837111432105303</v>
+        <v>0.05340230092406273</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.0001516352058388293</v>
+        <v>0.02993917837738991</v>
       </c>
       <c r="DO17" t="n">
-        <v>6.747440784238279e-05</v>
+        <v>0.06553232669830322</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.000395870505599305</v>
+        <v>0.06604017317295074</v>
       </c>
       <c r="DQ17" t="n">
-        <v>5.760592466685921e-05</v>
+        <v>0.1774471700191498</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.803221913287416e-05</v>
+        <v>0.04908962175250053</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0001713991514407098</v>
+        <v>0.125467836856842</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.000393688736949116</v>
+        <v>0.1357299834489822</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.0002804523683153093</v>
+        <v>0.005135471001267433</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.0002953697985503823</v>
+        <v>0.02154572866857052</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0001116859566536732</v>
+        <v>0.1082226932048798</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.0005167190684005618</v>
+        <v>0.01479187235236168</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.0005484931170940399</v>
+        <v>0.1896623820066452</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.0003140992776025087</v>
+        <v>0.03697655349969864</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0001866076199803501</v>
+        <v>0.04254052042961121</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.0002965701860375702</v>
+        <v>0.06074582785367966</v>
       </c>
       <c r="EC17" t="n">
-        <v>4.916237230645493e-05</v>
+        <v>0.02095223218202591</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0001938763889484107</v>
+        <v>0.07857082039117813</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.0005643114564009011</v>
+        <v>0.07947476208209991</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.0003085284261032939</v>
+        <v>0.03456936776638031</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.0009806362213566899</v>
+        <v>0.05655847489833832</v>
       </c>
       <c r="EH17" t="n">
-        <v>2.058153768302873e-05</v>
+        <v>0.03367466479539871</v>
       </c>
       <c r="EI17" t="n">
-        <v>9.908584615914151e-05</v>
+        <v>0.002629298716783524</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0002940794220194221</v>
+        <v>0.05576715618371964</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.0001955919142346829</v>
+        <v>0.005924379453063011</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0003964598290622234</v>
+        <v>0.004042655229568481</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.000125262959045358</v>
+        <v>0.007105153519660234</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0001944273826666176</v>
+        <v>0.07783053815364838</v>
       </c>
       <c r="EO17" t="n">
-        <v>1.74027809407562e-06</v>
+        <v>0.06369106471538544</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.0002862395776901394</v>
+        <v>0.03077790886163712</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.0008517169044353068</v>
+        <v>0.0696517676115036</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0006464264588430524</v>
+        <v>0.135765865445137</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.0005100840353406966</v>
+        <v>0.03546599298715591</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.000285099318716675</v>
+        <v>0.02108323574066162</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.0007534079486504197</v>
+        <v>0.08627346158027649</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.0006804597214795649</v>
+        <v>0.01585741713643074</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0001485942921135575</v>
+        <v>0.0175912044942379</v>
       </c>
       <c r="EX17" t="n">
-        <v>6.992192356847227e-05</v>
+        <v>0.05838491395115852</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.000610527815297246</v>
+        <v>0.1179460361599922</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.0003035073459614068</v>
+        <v>0.0428655669093132</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0001530859590275213</v>
+        <v>0.03202036768198013</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.0002205468190368265</v>
+        <v>0.04072099179029465</v>
       </c>
       <c r="FC17" t="n">
-        <v>9.784771827980876e-05</v>
+        <v>0.09712082892656326</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.000501415051985532</v>
+        <v>0.02519059553742409</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.0002362369268666953</v>
+        <v>0.03454232215881348</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.0004561185778584331</v>
+        <v>0.05139618739485741</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.0001783641346264631</v>
+        <v>0.1265691220760345</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.0001418071042280644</v>
+        <v>0.1214171722531319</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.0008400760125368834</v>
+        <v>0.08447027951478958</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0003988308599218726</v>
+        <v>0.08119110763072968</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0001282382727367803</v>
+        <v>0.004139553755521774</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.0002482130366843194</v>
+        <v>0.06120449304580688</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.0002801127557177097</v>
+        <v>0.06891468167304993</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.0002578357234597206</v>
+        <v>0.03118514083325863</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.0003062936884816736</v>
+        <v>0.005248634144663811</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0001880079798866063</v>
+        <v>0.06060076132416725</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0003384627343621105</v>
+        <v>0.2474936842918396</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.0007204352295957506</v>
+        <v>0.1975973844528198</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.0007001301273703575</v>
+        <v>0.1006009429693222</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.0006323480047285557</v>
+        <v>0.008848104625940323</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0003623912925831974</v>
+        <v>0.06158459931612015</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.0005607015336863697</v>
+        <v>0.1334180533885956</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.0001146009672083892</v>
+        <v>0.05734644830226898</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.0001861560886027291</v>
+        <v>0.02585142478346825</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.0008420113008469343</v>
+        <v>0.009196218103170395</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0002966542670037597</v>
+        <v>0.09940753877162933</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0002427469298709184</v>
+        <v>0.08823733776807785</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.0001203264837386087</v>
+        <v>0.01837365329265594</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.0003346983867231756</v>
+        <v>0.09542708843946457</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0004837640444748104</v>
+        <v>0.05112777650356293</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.001055579516105354</v>
+        <v>0.08455991744995117</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0001019320770865306</v>
+        <v>0.02619901672005653</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0001326041237916797</v>
+        <v>0.01909528858959675</v>
       </c>
     </row>
     <row r="18">
